--- a/data/scan_viz/review.xlsx
+++ b/data/scan_viz/review.xlsx
@@ -20,6 +20,9 @@
     <sheet name="test3_catalog_v2" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="test4_catalog_v2" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="test5_catalog_v2" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="test6_full_viz" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="test6_after_dedup" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="run1" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -9459,6 +9462,4747 @@
           <t>The crop image matches the 'samyang_cream_carbonara_140' product. Specifically, it features the distinct pink and yellow color scheme, the text 'Buldak' and 'Cream carbonara', and the identical character illustration and food serving suggestion as shown in the reference image.</t>
         </is>
       </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>crop_01_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>samyang_cheese_140</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8773151040077209</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>samyang_cheese_140:0.88, samyang_org_140:0.84, samyang_cream_carbonara_140:0.80, samyang_chacharoni_140:0.79, otoki_cheese:0.75</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The crop image matches the 'samyang_cheese_140' reference image perfectly. The key identifying features are the character (the chicken) eating a piece of yellow cheese, the yellow packaging background, the specific stylized 'Cheese' text, and the Korean text '치즈 불닭볶음면'. These elements align exactly with the Samyang Buldak Cheese 140g packaging.</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>crop_02_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>otoki_cheese</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8150874376296997</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>otoki_cheese:0.82, otoki_cheese_cay:0.77, indomie_dacbiet:0.72, nissin_gaccay:0.72, siukay_gaphomai_goi:0.71</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The crop shows packaging with the text 'OTOKI' and 'CHEESY', and clearly features the text 'VỊ PHÔ MAI CHEDDAR'. Comparing this to the reference images, it matches the Otoki Cheesy Ramen ('otoki_cheese') packaging perfectly. Other candidates are easily ruled out by brand name and package design differences.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>crop_03_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>otoki_cheese_cay</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8847552537918091</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>otoki_cheese_cay:0.88, otoki_cheese:0.82, denhat_thitbam:0.75, nissin_gaccay:0.75, koreno_prem_kimchi:0.75</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The crop shows a black packaging with the brand 'OTOKI' and the text 'MÌ TRỘN CHEESY' and 'VỊ PHÔ MAI CHEDDAR CAY'. This matches the reference image for 'otoki_cheese_cay' exactly.</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>crop_04_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>samyang_org_140</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.857998251914978</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>samyang_org_140:0.86, samyang_cream_carbonara_140:0.79, samyang_cheese_140:0.77, samyang_chacharoni_140:0.77, shin_org_goi_120:0.75</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The crop displays the iconic black packaging of the Samyang Buldak Hot Chicken Flavor Ramen (original). It features the distinct 'angry' character with a spiral on its cheek, the fire-breathing animation, and the overall design matches the samyang_org_140 reference image exactly.</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>crop_05_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dalatmilk_less_180</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6226761937141418</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>dalatmilk_less_180:0.62, th_probiotic_org_85:0.60, pepsi_org_lon_320:0.60, aquafina_5l:0.59, lavie_org_chai_1l5:0.57</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The crop displays a stack of product packaging with a blue and white design featuring the Dalat Milk brand. The partial text and specific graphical layout of the cow and landscape on the packaging matches the reference image for the 180ml Dalat Milk Less Sugar product.</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>crop_06_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>th_probiotic_org_85</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5399167537689209</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>aquafina_5l:0.58, lavie_org_chai_1l5:0.56, dalatmilk_less_180:0.55, pepsi_org_lon_320:0.55, th_probiotic_org_85:0.54</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The crop shows a blurry image, but the distinct silhouette and structural design of the product in the center clearly match the bottle shape of the 'th_probiotic_org_85' (TH True Yogurt Probi 85ml). The white color and the specific curvature of the top and bottom of the bottle in the crop are characteristic of this product.</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>crop_07_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>samyang_chacharoni_140</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8731816411018372</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>samyang_chacharoni_140:0.87, samyang_org_140:0.84, shin_org_goi_120:0.81, jin_jjajang_goi_135:0.80, chapagetti_goi_137:0.78</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>The product in the crop image is 'Samyang Chacharoni' based on the prominent, bold Korean text '짜짜로니' (Chacharoni) and the golden olive oil seal graphic on the right side. This matches the 'samyang_chacharoni_140' reference image perfectly in design, brand, and layout.</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>crop_08_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8982495665550232</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135:0.90, samyang_chacharoni_140:0.77, samyang_org_140:0.76, shin_org_goi_120:0.75, chapagetti_goi_137:0.74</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The crop image clearly displays the Ottogi logo and the text 'Jin jjajang', which matches the 'jin_jjajang_goi_135' reference image exactly in terms of design, branding, and text layout.</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>crop_09_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>otoki_yeul_kimchi_goi_100</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.882205069065094</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>otoki_yeul_kimchi_goi_100:0.88, shin_org_goi_120:0.74, samyang_org_140:0.74, nissin_gaccay:0.73, otoki_cheese_cay:0.73</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The crop displays the packaging for 'Mì Yeul Kimchi' by Otoki. Comparing this to the reference images, the design, including the Otoki logo, the text 'REAL KIMCHI CAY' and 'Mi YEUL', matches the 'otoki_yeul_kimchi_goi_100' candidate perfectly.</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>crop_10_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.89768385887146</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi:0.90, samyang_org_140:0.78, shin_org_goi_120:0.78, samyang_chacharoni_140:0.77, indomie_dacbiet:0.76</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>The crop image clearly displays the brand name 'KORENO' in large yellow text on an orange background, matching the packaging design of the 'koreno_prem_kimchi' reference image. The text 'MÌ VỊ KIM CHI' is also partially visible on the bottom left of the crop, confirming it as the Koreno Premium Kimchi instant noodle product.</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>crop_11_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>shin_org_goi_120</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8101075291633606</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>shin_org_goi_120:0.81, samyang_org_140:0.75, samyang_chacharoni_140:0.73, chapagetti_goi_137:0.72, samyang_cream_carbonara_140:0.70</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>The crop displays the distinctive red packaging and the large Chinese character '辛' associated with the Shin Ramyun brand. While it features a promotional image of a person (K-pop idol), which is a common marketing variation for Shin Ramyun, the logo, branding ('SHIN RAMYUN'), and color scheme correspond to the Shin Ramyun product line.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>crop_12_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pepsi_zero_lon_320</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5767812728881836</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>oreo_vanil_105:0.63, pepsi_org_lon_320:0.61, pepsi_org_chai_390:0.61, milo_org_180:0.59, pepsi_zero_lon_320:0.58</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>The crop shows a black Pepsi can with the text 'KHÔNG ĐƯỜNG', which matches the reference image for 'pepsi_zero_lon_320'.</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>crop_13_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>coca_org_chai_390</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5072760581970215</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>pepsi_org_lon_320:0.52, aquafina_5l:0.52, coca_zero_chai_390:0.51, coca_org_chai_390:0.51, pepsi_org_chai_390:0.50</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>The crop shows a vertical red section with text on it, which matches the characteristic side label design of a Coca-Cola product. Comparing this to the Coca-Cola variants provided, the red background and distinct white script styling are consistent with the Coca-Cola original formula branding (coca_org_chai_390).</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>crop_14_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>milo_org_180</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5962455868721008</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>oreo_vanil_105:0.63, pepsi_org_chai_390:0.61, dalatmilk_less_180:0.61, pepsi_org_lon_320:0.61, milo_org_180:0.60</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>The product in the crop shows the characteristic green packaging of the Milo brand. Specifically, the visual elements, color scheme, and the recognizable Milo branding layout match the 'milo_org_180' reference image, which represents the 180ml Milo barley milk drink.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>crop_15_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>mirinda_xaxi_chai_390</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5120696425437927</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>oreo_vanil_105:0.57, pepsi_org_lon_320:0.54, pepsi_org_chai_390:0.52, pepsi_org_chai_600:0.51, mirinda_xaxi_chai_390:0.51</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>The crop shows a package with visible text 'Mirinda' and 'Xá Xị' (partially visible as 'xaxi'). Comparing this with the provided references, the logo and design match the 'mirinda_xaxi_chai_390' bottle product.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>crop_16_ok.jpg</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.5793892741203308</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pepsi_org_lon_320:0.58, oreo_vanil_105:0.57, dalatmilk_less_180:0.56, pepsi_org_chai_390:0.56, aquafina_5l:0.56</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The visible part of the product in the crop shows a red and white packaging design with a texture that looks like a food item, possibly a snack or meat product, which does not match the packaging of any of the provided candidates (Pepsi, Oreo, Dalat Milk, or Aquafina).</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>crop_17_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8342082500457764</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137:0.83, samyang_chacharoni_140:0.76, shin_org_goi_120:0.73, samyang_org_140:0.72, jin_jjajang_goi_135:0.71</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>The crop image shows a pack of 'Chapagetti' with 'Spicy' branding, matching the 'chapagetti_goi_137' reference image. Key features include the 'Nongshim' logo, the large 'Chapagetti' brand text, and the 'SPICY' label on the red background, confirming it is the Nongshim Chapagetti spicy version.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>crop_18_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8905280232429504</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.89, siukay_haisan_goi:0.80, siukay_bo_goi:0.80, samyang_org_140:0.73, samyang_cream_carbonara_140:0.73</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>The crop image shows the yellow packaging of 'SiuKay' branded instant noodles with the text 'GÀ XỐT PHÔ MAI' visible, along with the character graphic matching the 'siukay_gaphomai_goi' reference image exactly.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>crop_19_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>siukay_bo_goi</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8790245056152344</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>siukay_bo_goi:0.88, siukay_gaphomai_goi:0.84, siukay_haisan_goi:0.82, samyang_org_140:0.78, samyang_cream_carbonara_140:0.75</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>The crop image shows the product packaging with the brand name 'SiuKay' and the text 'Hương vị Bò' (Beef flavor). This matches the reference image for 'siukay_bo_goi' exactly.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>crop_20_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>lays_tao_nori_53</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5498285293579102</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>oreo_vanil_105:0.59, pepsi_org_lon_320:0.57, pepsi_org_chai_390:0.57, dalatmilk_less_180:0.56, lays_tao_nori_53:0.55</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>The crop shows a green packaging with the distinctive Lay's logo and sushi graphic, which matches the Lay's Nori Seaweed (vị tảo biển Nori) product. The text 'Vị Tảo Biển Nori' is visible on the package in the crop, confirming it matches the 'lays_tao_nori_53' reference image.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>crop_21_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>siukay_haisan_goi</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8329233527183533</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.84, siukay_haisan_goi:0.83, siukay_bo_goi:0.81, samyang_org_140:0.73, haohao_hanhtim:0.73</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>The crop displays the 'SiuKay' brand logo, 'Hương vị Hải Sản' text, and an image of a squid on a black background, which perfectly matches the 'siukay_haisan_goi' reference image.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>crop_22_ok.jpg</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.7279926538467407</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>samyang_org_140:0.73, siukay_gaphomai_goi:0.72, denhat_photron_cay_goi:0.72, denhat_thitbam:0.71, haohao_hanhtim:0.71</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>The crop displays text that reads 'THẦN ỚT' and 'XỐT CUA ỚT'. None of the provided reference images match this branding or flavor. The product name 'THẦN ỚT' is clearly visible in the crop, and it is not among the listed options (Samyang, Siukay, De Nhat, or Hao Hao). Therefore, it must be 'unknown'.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>crop_23_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>siukay_haisan_goi</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7745076417922974</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.82, siukay_haisan_goi:0.77, siukay_bo_goi:0.76, denhat_thitbam:0.74, haohao_prem_bosate:0.71</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>The visible text on the packaging includes 'SiuKay' and 'An dang MI XAO, MI NUOC deu ngon!'. Among the options, the 'siukay_gaphomai_goi', 'siukay_haisan_goi', and 'siukay_bo_goi' all have this specific branding and descriptive text. However, comparing the background design and the food imagery in the crop with the provided reference images, the specific color and visual style match the 'siukay_haisan_goi' reference, specifically the black background with yellow lightning-like accents, which is distinct from the yellow-orange of the cheese variant or the dark red of the beef variant.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>crop_24_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nissin_gaccay</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.833653450012207</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>nissin_gaccay:0.83, samyang_org_140:0.74, siukay_gaphomai_goi:0.72, otoki_cheese_cay:0.72, siukay_haisan_goi:0.71</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>The crop image matches the 'nissin_gaccay' reference image perfectly, displaying the 'NISSIN' brand logo, the 'mì cay' branding, and the 'GÀ CAY PHÔ MAI' text, along with the distinct graphic of the chicken and cheese on the packaging.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>crop_25_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>indomie_caynong</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7328441739082336</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>indomie_caynong:0.73, indomie_dacbiet:0.72, denhat_thitbam:0.71, samyang_org_140:0.68, siukay_bo_goi:0.68</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>The crop image shows the packaging of an 'Indomie' instant noodle product. The text 'Mi goreng' and 'cay nong' are visible on the right side of the packaging. Comparing this with the provided candidates, it matches exactly the 'indomie_caynong' (Mì xào cay nồng) product packaging, including the layout and color scheme.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>crop_26_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>indomie_caynong</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7981555461883545</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.81, indomie_caynong:0.80, denhat_thitbam:0.75, indomie_hypeabis:0.75, haohao_mixao_haisan:0.73</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>The crop displays the Indomie brand and the text 'Mi goreng Pedas' along with 'vị cay nồng' and 'mì xào khô'. Comparing this to the reference images, it matches the packaging of 'indomie_caynong' (Mi xào cay nồng Indomie) exactly, including the specific weight '79g' printed at the bottom.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>crop_27_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>indomie_caynong</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7637370228767395</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.79, denhat_thitbam:0.79, indomie_caynong:0.76, indomie_hypeabis:0.73, koreno_prem_kimchi:0.72</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>The crop displays the classic 'Indomie' logo, and the visible text 'Mi goreng' along with the color scheme confirms it is an Indomie product. Comparing it to the reference images, the specific packaging style and the partial Vietnamese text 'cay nồng' (meaning 'spicy') clearly identifies this as the 'indomie_caynong' (Mi xào khô vị cay nồng).</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>crop_28_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.8510382175445557</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.85, indomie_hypeabis:0.78, indomie_caynong:0.78, denhat_thitbam:0.77, koreno_prem_kimchi:0.73</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>The visible text 'Indomie' and 'Mi Goreng' on the packaging, along with the distinctive color scheme and graphical elements like the egg, match the reference image for 'indomie_dacbiet' exactly.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>crop_29_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.8159981369972229</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.82, denhat_thitbam:0.77, indomie_caynong:0.76, haohao_mixao_haisan:0.73, indomie_hypeabis:0.73</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>The crop displays the characteristic Indomie branding and packaging design for 'Mi Goreng' (Fried Noodles). Comparing it with the reference images, it matches the Indomie 'dacbiet' variant perfectly, specifically the design showing the noodles, the egg, and the 'Mi goreng' text on the red background.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>crop_30_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.8703043460845947</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate:0.87, haohao_hanhtim:0.83, haohao_prem_tomchuacay:0.82, haohao_mixao_haisan:0.80, haohao_tomchuacay:0.79</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>The crop image shows a product with 'PREMIUM' printed prominently, along with the text 'MÌ TRỘN BÒ SA TẾ' and 'Gói súp lớn'. Comparing this to the reference images, it matches the 'haohao_prem_bosate' product exactly in terms of design, text, and flavor branding.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>crop_31_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.8608794212341309</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate:0.86, haohao_prem_tomchuacay:0.82, haohao_hanhtim:0.82, haohao_tomchuacay:0.80, haohao_mixao_haisan:0.80</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>The crop image shows 'Hảo Hảo' and 'PREMIUM' branding, along with the text 'HƯƠNG VỊ MÌ TRỘN BÒ SA TẾ'. Comparing this to the reference images, it perfectly matches the 'haohao_prem_bosate' product.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>crop_32_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>haohao_prem_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.864803671836853</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate:0.87, haohao_prem_tomchuacay:0.86, haohao_hanhtim:0.84, haohao_tomchuacay:0.83, haohao_mixao_haisan:0.81</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>The product in the image is clearly labeled 'PREMIUM' and 'HƯƠNG VỊ MÌ TÔM CHUA CAY'. By comparing this to the provided reference images, it matches the 'haohao_prem_tomchuacay' SKU, which features the same gold and pink color scheme, 'PREMIUM' text, and 'MÌ TÔM CHUA CAY' flavor designation.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>crop_33_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.8178182244300842</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.82, haohao_mixao_tomchuangot:0.80, haohao_hanhtim:0.77, haohao_mixao_haisan:0.77, denhat_thitbam:0.76</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>The crop shows a packaging with the text 'Hảo Hảo' and 'Rau Nấm'. This matches the 'Mì Hảo Hảo chay rau nấm' (haohao_chay) product. The visual elements, such as the text 'Rau Nấm' and the overall green theme, are consistent with the haohao_chay reference image.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>crop_34_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.8065701127052307</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>haohao_hanhtim:0.82, haohao_tomchuacay:0.81, haohao_mixao_haisan:0.79, haohao_chay:0.79, haohao_mixao_tomchuangot:0.78</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>The crop shows the packaging text 'MÌ TÔM CHUA CAY' and the brand 'Hảo Hảo'. Comparing this to the reference images, the design and text match perfectly with the 'haohao_tomchuacay' reference image.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>crop_35_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.8692145943641663</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay:0.87, haohao_hanhtim:0.85, haohao_mixao_haisan:0.83, haohao_prem_tomchuacay:0.83, haohao_mixao_tomchuangot:0.82</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The crop image shows the packaging of Hảo Hảo Mì Tôm Chua Cay, identifiable by the distinct pink packaging color and the text 'MÌ TÔM CHUA CAY' visible on the right side. The overall graphic, including the shrimp and lime motif, matches the reference image for 'haohao_tomchuacay' exactly.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>crop_36_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>koreno_volcano</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.9165272116661072</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>koreno_volcano:0.92, koreno_prem_kimchi:0.77, samyang_org_140:0.75, samyang_chacharoni_140:0.73, haohao_mixao_haisan:0.73</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>The product in the image is clearly labeled 'VOLCANO' and 'Mì xào KORENO'. Comparing this to the reference images, it matches perfectly with 'koreno_volcano', showing the same chicken mascot and color scheme.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>crop_37_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>omachi_spa_goi</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.8542584776878357</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>omachi_spa_goi:0.85, omachi_tomchuacay_goi:0.75, omachi_suonham_goi:0.73, denhat_thitbam:0.71, siukay_gaphomai_goi:0.69</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>The crop shows the packaging of 'Mì trộn Omachi xốt Spaghetti'. Key text elements such as 'Omachi', 'Xốt Spaghetti', 'XỐT BÒ BẦM CÀ CHUA', and 'THÊM GÓI PHÔ MAI' perfectly match the 'omachi_spa_goi' reference image.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>crop_38_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8352421522140503</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.84, haohao_mixao_tomchuangot:0.77, haohao_tomchuacay:0.77, haohao_hanhtim:0.77, haohao_mixao_haisan:0.77</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>The packaging in the provided image clearly displays the text 'Hương vị RAU NẤM', which translates to 'Mushroom and vegetable flavor'. Comparing this with the reference images, it matches the 'haohao_chay' (Mì Hảo Hảo chay rau nấm) product perfectly, which also features a green design and the text 'hương vị RAU NẤM'.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>crop_39_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>haohao_mixao_tomchuangot</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.843750536441803</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>haohao_mixao_tomchuangot:0.84, haohao_mixao_haisan:0.81, haohao_hanhtim:0.76, haohao_tomchuacay:0.75, haohao_prem_bosate:0.74</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>The crop image shows the packaging for 'Hảo Hảo Mì Xào' with the flavor text 'Tôm Xào Chua Ngọt' clearly visible. This matches the branding, design elements (green and yellow packaging), and product name of the 'haohao_mixao_tomchuangot' reference image.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>crop_40_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>haohao_mixao_haisan</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8731926083564758</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>haohao_mixao_haisan:0.87, haohao_mixao_tomchuangot:0.84, haohao_hanhtim:0.83, denhat_thitbam:0.81, haohao_tomchuacay:0.81</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>The crop image shows the product packaging with the text 'Hảo Hảo', 'Mì Xào', and 'hương vị HẢI SẢN'. This matches the reference image for 'haohao_mixao_haisan' perfectly.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>crop_41_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>haohao_hanhtim</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8718258142471313</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>haohao_hanhtim:0.87, haohao_mixao_haisan:0.81, haohao_prem_bosate:0.80, haohao_prem_tomchuacay:0.79, haohao_tomchuacay:0.78</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>The product in the image is clearly labeled 'hương vị SA TẾ HÀNH TÍM'. Comparing this to the reference images, it matches the design, color scheme, and text of the 'haohao_hanhtim' (Mì Hảo Hảo sa tế hành tím) product exactly.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>crop_42_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>omachi_tomchuacay_goi</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.8114017844200134</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>omachi_tomchuacay_goi:0.81, omachi_suonham_goi:0.78, omachi_spa_goi:0.73, otoki_yeul_kimchi_goi_100:0.67, denhat_photron_cay_goi:0.67</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The crop image shows the Omachi brand logo and partial text 'Tôm Càng' and 'chua cay'. This matches the packaging design and product name of the Omachi lẩu tôm càng flavour.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>crop_43_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>mi_lauthaitom_goi</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.7828880548477173</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>mi_lauthaitom_goi:0.78, haohao_tomchuacay:0.71, denhat_thitbam:0.69, haohao_prem_tomchuacay:0.68, haohao_hanhtim:0.68</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>The crop shows text 'LẦU THÁI' and 'Hương vị TÔM' which matches the design of the 'mi_lauthaitom_goi' reference image perfectly.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>crop_44_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>omachi_suonham_goi</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.7796948552131653</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>omachi_suonham_goi:0.78, omachi_tomchuacay_goi:0.76, denhat_thitbam:0.74, denhat_photron_cay_goi:0.71, phuhuong_thitbam_goi:0.71</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>The crop image features the brand 'Omachi' and part of the text 'Sườn' which is clearly visible. Comparing this to the reference images, the design and color scheme (purple and black) match the Omachi Sườn Hầm Ngũ Quả packaging perfectly.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>crop_45_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6858667731285095</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>haohao_prem_tomchuacay:0.70, haohao_tomchuacay:0.69, haohao_big100:0.68, siukay_gaphomai_goi:0.67, omachi_tomchuacay_goi:0.65</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>The crop displays the characteristic design of the Hảo Hảo brand's Tom Cay Chua flavour. Specifically, the logo text 'Hảo Hảo' and the large text 'Tom Cay Chua' with the imagery of a prawn are identical to the 'haohao_tomchuacay' reference. The specific composition of the ingredients (shrimp, lime slice) and the font style on the packaging match the standard Hảo Hảo 75g package.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>crop_46_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>denhat_thitbam</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.9126074910163879</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>denhat_thitbam:0.91, denhat_phobo_goi:0.76, denhat_photron_bo_goi:0.76, denhat_photron_cay_goi:0.75, haohao_mixao_haisan:0.75</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>The crop image shows the text 'ĐỆ NHẤT', 'MÌ GIA', and 'THỊT BẰM'. Comparing this with the provided reference images, it matches exactly with the packaging design, branding, and flavor label of the 'denhat_thitbam' (Mì Đệ Nhất thịt bằm) product.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>crop_47_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>mi_lauthaitom_goi</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.8527869582176208</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>mi_lauthaitom_goi:0.85, haohao_tomchuacay:0.73, denhat_thitbam:0.73, haohao_hanhtim:0.73, haohao_mixao_haisan:0.72</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>The crop image shows the text 'MÌ LẤU THÁI' and 'Hương vị TÔM', which matches exactly with the reference image for 'mi_lauthaitom_goi'.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>crop_48_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>udon_sukisuki_tron</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.8536402583122253</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>udon_sukisuki_tron:0.85, udon_sukisuki_goi:0.77, denhat_photron_bo_goi:0.74, denhat_photron_cay_goi:0.73, haohao_prem_bosate:0.72</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>The crop image shows the product 'Udon' with 'SUKISUKI' branding, 'Trộn' (mixed noodles) text, and 'HƯƠNG VỊ BÒ XỐT TERIYAKI'. Comparing this to the provided reference images, it is an exact match for the 'udon_sukisuki_tron' SKU.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>crop_49_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>udon_sukisuki_tron</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.805508553981781</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>udon_sukisuki_tron:0.81, udon_sukisuki_goi:0.74, denhat_photron_bo_goi:0.69, vifon_bocay_goi:0.67, haohao_prem_bosate:0.67</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>The crop shows the text 'Udon', 'SUKISUKI', and 'Trộn' as well as 'HƯƠNG VỊ BÒ XỐT TERIYAKI'. This perfectly matches the packaging design and labels of the udon_sukisuki_tron reference image.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>crop_50_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>haohao_big100</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.8857532143592834</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>haohao_big100:0.89, haohao_tomchuacay:0.83, haohao_hanhtim:0.83, haohao_mixao_haisan:0.82, haohao_prem_tomchuacay:0.80</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>The image clearly shows the packaging for 'Hảo Hảo BIG' with '100g' prominently displayed. Comparing this to the candidate reference images, it matches the 'haohao_big100' packaging, which features the large 'BIG 100g' text and the 'TĂNG HƠN 30%' starburst graphic.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>crop_51_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>vifon_bocay_goi</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.9174304604530334</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>vifon_bocay_goi:0.92, vifon_rieucua_goi:0.76, denhat_thitbam:0.73, udon_sukisuki_tron:0.71, denhat_phobo_goi:0.71</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>The crop displays the Vifon brand logo and the text 'MÌ BÒ CAY' and 'THỊT THẬT', which matches the 'vifon_bocay_goi' reference image perfectly. The design, including the bowl of noodles and the placement of the text, is identical.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>crop_52_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>vifon_rieucua_goi</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.8894175887107849</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>vifon_rieucua_goi:0.89, denhat_thitbam:0.74, vifon_bocay_goi:0.74, otoki_cheese_cay:0.73, udon_sukisuki_goi:0.72</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>The product image clearly shows the 'VIFON' brand logo and the text 'Mì Riêu Cua' along with the English subtitle 'CRAB SOUP'. This matches the reference image for 'vifon_rieucua_goi' perfectly, including the packaging design, font, and imagery.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>crop_53_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>vifon_rieucua_goi</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.7097520232200623</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>vifon_rieucua_goi:0.71, otoki_cheese_cay:0.62, shin_org_goi_120:0.61, denhat_thitbam:0.61, samyang_org_140:0.61</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>The crop image shows the text 'CRAB SOU' (part of CRAB SOUP) and 'VIFON'. It also shows a badge with the text 'CÓ GÓI CUA THẬT' and a specific medal design that matches the reference image for 'vifon_rieucua_goi'. Other candidates are completely different in brand and packaging design.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>crop_54_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>denhat_photron_cay_goi</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.8382065892219543</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>denhat_photron_cay_goi:0.84, denhat_photron_bo_goi:0.81, denhat_thitbam:0.80, denhat_phobo_goi:0.78, haohao_hanhtim:0.77</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>The crop shows packaging with the text 'ĐỆ NHẤT', 'PHỞ', and 'THẬP CẨM CAY'. This matches the packaging design and product name of the 'denhat_photron_cay_goi' candidate.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>crop_55_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>denhat_phobo_goi</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.8567149639129639</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>denhat_phobo_goi:0.86, denhat_photron_bo_goi:0.75, denhat_thitbam:0.75, denhat_photron_cay_goi:0.74, omachi_tomchuacay_goi:0.70</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>The product in the crop clearly shows the text 'PHỞ BÒ' and 'ĐỆ NHẤT', matching the 'denhat_phobo_goi' candidate. The packaging design features the characteristic dark red background, '12h' logo, and bowl of soup, which aligns perfectly with the provided reference image for 'denhat_phobo_goi'.</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>crop_56_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>phuhuong_thitbam_goi</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.753035306930542</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>phuhuong_thitbam_goi:0.75, denhat_thitbam:0.74, phuhuong_suonheo_goi:0.72, nhipsong_namvang:0.71, denhat_photron_bo_goi:0.67</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>The product in the crop shows the brand name 'Miến Phú Hương' and the flavor text 'THỊT BẰM'. Comparing this to the reference images, it matches exactly with the packaging of the 'phuhuong_thitbam_goi' SKU.</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>crop_57_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>phuhuong_suonheo_goi</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.7130369544029236</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>phuhuong_suonheo_goi:0.71, phuhuong_thitbam_goi:0.69, haohao_mixao_tomchuangot:0.67, denhat_thitbam:0.65, haohao_chay:0.63</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>The crop image shows a product with 'Miến Phú Hương' and 'Hương vị SƯỜN HEO' text. By comparing this to the reference images, it matches the 'phuhuong_suonheo_goi' product exactly in terms of design, logo, and flavor text.</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>crop_58_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>nhipsong_namvang</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.8100965619087219</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>nhipsong_namvang:0.81, denhat_thitbam:0.74, phuhuong_suonheo_goi:0.74, phuhuong_thitbam_goi:0.73, haohao_prem_bosate:0.72</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>The crop displays the branding 'Nhịp Sống' and the text 'Hủ Tiếu Nam Vang', which matches exactly with the reference image for 'nhipsong_namvang'.</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>crop_59_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>phuhuong_suonheo_goi</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.6989503502845764</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>phuhuong_suonheo_goi:0.70, phuhuong_thitbam_goi:0.69, denhat_thitbam:0.64, denhat_phobo_goi:0.62, milo_org_180:0.62</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>The crop shows the 'Miến Phú Hương' brand name and parts of the packaging with green color tones. Comparing this with the candidates, the product design matches the 'phuhuong_suonheo_goi' (Miến Phú Hương sườn heo) reference image, specifically the green background and the 'Miến Phú Hương' branding style.</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>crop_file</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>predicted_sku_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>top5_candidates</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>llm_reasoning</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>true_sku_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>crop_00_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>otoki_cheese_cay</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7607427835464478</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>otoki_cheese:0.76, otoki_cheese_cay:0.76, samyang_org_140:0.72, denhat_thitbam:0.71, siukay_gaphomai_goi:0.71</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against the plausible cheese ramen options, the packaging clearly shows the text "VỊ PHÔ MAI CHEDDAR CAY" in a white burst shape and a black background with yellow "CHEESY" text, which matches the reference image for "otoki_cheese_cay" (Mì trộn vị phô mai cheddar cay Otoki 120g).</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>crop_01_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>otoki_cheese</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8444159626960754</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>otoki_cheese:0.84, otoki_cheese_cay:0.79, siukay_gaphomai_goi:0.73, denhat_thitbam:0.72, indomie_dacbiet:0.72</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The product packaging clearly displays the large text 'CHEESY' and 'RAMEN' with a yellow background, and the specific label 'VỊ PHÔ MAI CHEDDAR'. Comparing this against the candidate reference images, it matches the packaging of 'Mì phô mai cheddar Otoki 110g' (otoki_cheese) exactly, while differing from the black background of the spicy version (otoki_cheese_cay) and other candidates.</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>crop_02_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>samyang_cheese_140</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8778430819511414</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>samyang_cheese_140:0.88, samyang_org_140:0.85, samyang_cream_carbonara_140:0.81, samyang_chacharoni_140:0.81, otoki_cheese:0.77</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the candidate reference images, the packaging features a yellow background with the cartoon chicken character holding a large wedge of cheese and sitting on a cheese wheel, along with the distinctive Samyang Buldak Korean text in red and 'Cheese' written in white/blue. This precisely matches the packaging of 'samyang_cheese_140' (Mì Samyang Buldak khô gà cay vị phô mai 140g). Other yellow-themed noodles like 'otoki_cheese' lack the character and specific branding. Therefore, the confirmed item is samyang_cheese_140.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>crop_03_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>samyang_org_140</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8615518808364868</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>samyang_org_140:0.86, samyang_chacharoni_140:0.79, samyang_cream_carbonara_140:0.78, samyang_cheese_140:0.78, chapagetti_goi_137:0.76</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against the plausible candidates in the same black packaging category (samyang_org_140), the packaging features the classic black background with the white chicken character Hochi holding a bowl, along with the red Korean text and the pan of spicy noodles. This exactly matches the design of samyang_org_140.</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>crop_04_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>samyang_cream_carbonara_140</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8539941310882568</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>samyang_cream_carbonara_140:0.85, samyang_org_140:0.76, samyang_cheese_140:0.75, samyang_chacharoni_140:0.70, siukay_bo_goi:0.68</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The user provided a crop of a single retail product and a list of candidates. The packaging in the query image clearly shows the text 'Buldak' and 'Cream Carbonara', alongside the distinct pinkish-yellow color scheme and the mascot Hochi. Comparing it to the reference images, it matches the exact design of the samyang_cream_carbonara_140 product.</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>crop_05_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>samyang_org_140</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5722783207893372</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>samyang_org_140:0.57, samyang_cream_carbonara_140:0.56, maeil_nho:0.51, samyang_cheese_140:0.50, maeil_tao:0.49</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The cropped image shows the character 'Hochi' holding a small bowl with a spoon, wearing a spotted skirt, which matches the mascot artwork found on Samyang Buldak instant noodle packages. Comparing the candidates samyang_org_140, samyang_cream_carbonara_140, and samyang_cheese_140, the exact mascot pose with the bowl and spoon, along with the black background tone and white-spotted yellow skirt, matches the original Samyang Buldak packaging (samyang_org_140). Therefore, the correct product is samyang_org_140.</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>crop_06_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8309429883956909</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi:0.83, samyang_chacharoni_140:0.73, samyang_org_140:0.72, shin_org_goi_120:0.72, haohao_prem_bosate:0.72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The image crop clearly displays the large yellow text 'KORENO' with the word 'PREMIUM' underneath, matching the packaging design of the Koreno Premium Kimchi instant noodle product ('koreno_prem_kimchi'). All other candidates are successfully ruled out due to entirely different brand logos and product names.</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>crop_07_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>shin_org_goi_120</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7772074341773987</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>shin_org_goi_120:0.78, samyang_org_140:0.71, samyang_chacharoni_140:0.70, chapagetti_goi_137:0.69, jin_jjajang_goi_135:0.66</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>The user image displays the distinctive large Chinese character '辛' and the bold text 'SHIN RAMYUN' inside a yellow box alongside a red background, which matches the packaging design of 'shin_org_goi_120'. Comparing it against the other options, it clearly differs from the black packaging of Samyang or the yellow packaging of Jin Jjajang.</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>crop_08_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8556005358695984</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi:0.86, haohao_prem_bosate:0.73, haohao_hanhtim:0.73, indomie_dacbiet:0.73, denhat_thitbam:0.73</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The product image clearly displays the brand name "KORENO" in large yellow letters and the label "MÌ VỊ KIM CHI" at the bottom left, which matches the reference image for koreno_prem_kimchi.</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>crop_09_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>otoki_yeul_kimchi_goi_100</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8958897590637207</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>otoki_yeul_kimchi_goi_100:0.90, nissin_gaccay:0.71, samyang_org_140:0.70, siukay_bo_goi:0.70, shin_org_goi_120:0.70</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the reference images, the packaging features the brand 'OTOKI' at the top left and large text 'REAL KIMCHI CAY YYY' in yellow/white. This precisely matches the reference image for 'otoki_yeul_kimchi_goi_100' (Gói Mì Yeul Kimchi Cay Otoki 100g).</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>crop_10_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8916890621185303</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135:0.89, samyang_chacharoni_140:0.76, samyang_org_140:0.74, chapagetti_goi_137:0.74, shin_org_goi_120:0.74</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>The target image clearly shows the 'OTOKI' (Ottogi) logo at the top center and the large 'Jin jjajang' branding, which matches the packaging of 'Mì Jin Jjajang xốt tương đen Ottogi 135g' (jin_jjajang_goi_135). Comparing with the reference images, all key design elements, including the yellow background and typography, match this specific SKU.</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>crop_11_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>samyang_chacharoni_140</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8551577925682068</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>samyang_chacharoni_140:0.86, samyang_org_140:0.80, jin_jjajang_goi_135:0.77, shin_org_goi_120:0.76, chapagetti_goi_137:0.74</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the reference candidates, the packaging features the distinct dark brown background with green/yellow accents and the prominent yellow seal on the right reading 'EXTRA VIRGIN 100% Olive Oil' along with the large white Korean typography '짜짜로니'. This matches the reference image for samyang_chacharoni_140 precisely.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>crop_12_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8687357306480408</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135:0.87, samyang_chacharoni_140:0.72, denhat_thitbam:0.72, indomie_dacbiet:0.70, samyang_org_140:0.70</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Comparing the crop image to the candidate products, the packaging prominently displays the text "Jin jjajang" and "MÌ XỐT TƯƠNG ĐEN" in the upper right, directly matching the Jin Jjajang xốt tương đen Ottogi 135g packaging. This confirms jin_jjajang_goi_135 as the correct product.</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>crop_13_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7289931178092957</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>denhat_thitbam:0.77, indomie_dacbiet:0.73, koreno_prem_kimchi:0.73, samyang_chacharoni_140:0.72, samyang_org_140:0.71</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Comparing the crop image to the reference candidates, the packaging features orange background tones, black bottom area, and the text 'MÌ VỊ KIM CHI' matching the Koreno Premium Kimchi reference packaging ('koreno_prem_kimchi'), confirming the correct SKU.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>crop_14_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>koreno_volcano</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6655938625335693</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.69, nissin_gaccay:0.68, denhat_thitbam:0.67, siukay_bo_goi:0.67, koreno_volcano:0.67</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Comparing the crop image to the candidate products, we see the prominent yellow text 'CAY YYY' and the black/red packaging background. Among the candidates, koreno_volcano has black packaging with red and yellow text ('CAY CỰC ĐÃ' and 'VOLCANO Mì xào KORENO'). The crop matches the exact design elements from the Koreno Volcano packaging.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>crop_15_ok.jpg</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7200273871421814</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.72, samyang_org_140:0.72, denhat_photron_cay_goi:0.71, denhat_photron_bo_goi:0.71, denhat_thitbam:0.70</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>The target product image clearly shows the text "THẦN ỚT" on the packaging along with an angry chili character holding a flame, and the logo "NẤU PHÚ". None of the provided reference candidates (siukay_gaphomai_goi, samyang_org_140, denhat_photron_cay_goi, denhat_photron_bo_goi, denhat_thitbam) match this branding or packaging design. Therefore, the product must be classified as unknown.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>crop_16_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>siukay_haisan_goi</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8281581401824951</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.84, siukay_haisan_goi:0.83, siukay_bo_goi:0.78, nissin_gaccay:0.69, haohao_prem_bosate:0.68</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The product packaging features the Acecook logo and the prominent 'SiuKay' brand name in yellow lettering with a red chili icon, alongside a black and white background. Looking at the flavor label on the bottom left, it clearly reads 'Hương vị Hải Sản' (Seafood Flavour) with an image of a squid, which matches the reference image for 'siukay_haisan_goi' perfectly.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>crop_17_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8477725386619568</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137:0.85, samyang_chacharoni_140:0.78, samyang_org_140:0.73, jin_jjajang_goi_135:0.71, shin_org_goi_120:0.69</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Comparing the crop against the candidates, the package clearly displays the 'Chapagetti' brand name and the 'SPICY' red badge on the left, matching the Nongshim Chapagetti Spicy 137g (chapagetti_goi_137) perfectly.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>crop_18_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>siukay_bo_goi</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8480976223945618</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>siukay_bo_goi:0.85, siukay_gaphomai_goi:0.84, siukay_haisan_goi:0.82, samyang_org_140:0.74, nissin_gaccay:0.73</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>The crop displays the iconic 'SiuKay' brand logo in yellow with a red chili accent, alongside a cartoon cow and the text 'Hương vị Bò' (Beef flavor) characteristic of the siukay_bo_goi SKU. By comparing this with reference candidates, it directly matches the Acecook SiuKay Beef flavor packaging rather than the chicken/cheese or seafood variants.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>crop_19_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8781773447990417</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.88, siukay_haisan_goi:0.78, siukay_bo_goi:0.76, samyang_cream_carbonara_140:0.70, nissin_gaccay:0.70</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>The product packaging shown in the query image features the distinct 'SiuKay' logo with a chili pepper embedded in the letter 'S', the Acecook logo in the top left corner, and the text 'GÀ XỐT PHÔ MAI'. This matches the reference image for 'siukay_gaphomai_goi' perfectly, ruling out other options like Nissin or Samyang.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>crop_20_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.8182909488677979</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137:0.82, samyang_chacharoni_140:0.79, samyang_org_140:0.77, jin_jjajang_goi_135:0.73, siukay_haisan_goi:0.71</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>The query crop clearly displays the packaging text 'Chapagetti' along with the Korean characters '매콤한 짜파게티' and a red 'SPICY' chili logo on a dark background, which matches the Nongshim Chapagetti Spicy 137g package (chapagetti_goi_137). Comparing it against other variants like Samyang Chacharoni or Jin Jjajang, the specific brand and layout confirm chapagetti_goi_137.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>crop_21_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>indomie_caynong</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6919452548027039</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.70, indomie_caynong:0.69, denhat_thitbam:0.68, denhat_photron_bo_goi:0.65, jin_jjajang_goi_135:0.64</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Comparing the crop image to the reference options, the packaging prominently displays 'Mi goreng Pedas' and 'vị cay nồng' with the distinctive Indomie logo and magenta/red color scheme, perfectly matching the 'indomie_caynong' reference image.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>crop_22_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.6598984599113464</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>indomie_caynong:0.67, indomie_dacbiet:0.66, denhat_thitbam:0.65, samyang_org_140:0.63, samyang_cream_carbonara_140:0.63</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Comparing the crop with the plausible candidates, we can see the classic Indomie logo at the bottom right corner ('Indo-mie') along with the green banner containing 'stant Noodles' and the 'Mi Goreng' text in pink/red with a black plate of noodles and vegetables. Looking closely at the visible wording and background elements, it matches the Indomie Mi Goreng special variety (indomie_dacbiet).</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>crop_23_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8253313302993774</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.83, denhat_thitbam:0.78, indomie_caynong:0.78, indomie_hypeabis:0.74, koreno_prem_kimchi:0.72</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Comparing the user's cropped image against the candidates, the packaging clearly shows the Indomie logo and the text 'Mi goreng' alongside 'Vị đặc biệt'. This matches the reference image for 'indomie_dacbiet', confirming the product.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>crop_24_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>indomie_caynong</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.7986646890640259</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.81, indomie_caynong:0.80, denhat_thitbam:0.77, indomie_hypeabis:0.75, koreno_prem_kimchi:0.69</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>The crop image shows a product with the characteristic 'Indomie' logo in blue on a red background and packaging features resembling the Indomie instant noodles lineup. Comparing against plausible candidates like indomie_dacbiet, indomie_caynong, and indomie_hypeabis, the text visible in the bottom-left corner of the crop reads 'i reng das' (partially matching 'Mi goreng pedas' or similar variation like indomie_caynong). Looking at the red top header with white and blue Indomie logo and the specific layout of the chili peppers and textual elements, it matches indomie_caynong.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>crop_25_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nissin_gaccay</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8427699208259583</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>nissin_gaccay:0.84, siukay_gaphomai_goi:0.75, siukay_bo_goi:0.74, siukay_haisan_goi:0.73, indomie_dacbiet:0.72</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the provided candidates, we can see the packaging prominently features the red 'NISSIN' logo and the text 'MÌ CAY NISSIN', with the bottom right indicating 'HƯƠNG VỊ GÀ CAY PHÔ MAI'. This matches the reference image for 'nissin_gaccay' (Mì xào Nissin gà cay phô mai Hàn Quốc 72g) precisely, and rules out the other brand candidates such as SiuKay or Indomie.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>crop_26_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.8060095310211182</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.81, indomie_caynong:0.75, denhat_thitbam:0.75, indomie_hypeabis:0.73, haohao_mixao_haisan:0.70</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>The product image clearly shows the iconic red and green logo of 'Indomie' along with the text 'Mi Goreng' and 'Fried Noodles'. By comparing it with the plausible reference images, the packaging design and text match the 'indomie_dacbiet' (Mì xào khô đặc biệt Indomie gói 85g), specifically showing the fried egg and noodle illustration in the bottom right corner characteristic of this version.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>crop_27_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.8246777653694153</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.82, denhat_thitbam:0.78, indomie_caynong:0.77, indomie_hypeabis:0.74, haohao_mixao_haisan:0.72</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the candidate references, the packaging clearly displays the blue 'Indomie' logo, 'Instant Noodles', and the 'Mi Goreng' label with a fried egg and shrimp serving suggestion. This matches the 'indomie_dacbiet' reference image (Mì xào khô đặc biệt Indomie gói 85g), while other candidates like Indomie cay nồng or Hype Abis have different color schemes or extra text ('Pedas', 'Hype Abis') that are absent here.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>crop_28_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7703028321266174</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.77, haohao_mixao_tomchuangot:0.75, denhat_thitbam:0.74, haohao_hanhtim:0.73, haohao_tomchuacay:0.73</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>The query crop shows the distinctive green packaging, the 'Hảo Hảo' logo, and text matching 'Mì Chay' with mushroom and leaf graphics characteristic of the vegetarian Hảo Hảo variant. Comparing this to the reference images, it clearly matches the 'haohao_chay' (Mì Hảo Hảo chay rau nấm 74g) reference image.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>crop_29_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.8351150751113892</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay:0.84, haohao_hanhtim:0.81, haohao_prem_tomchuacay:0.81, haohao_mixao_haisan:0.80, haohao_chay:0.78</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against the reference candidates, the packaging features the classic pink background with the 'Hảo Hảo' brand name and the text 'MÌ TÔM CHUA CAY' along with the 1/3 canxi supplement badge on the bottom right. This matches the standard 'haohao_tomchuacay' packaging precisely.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>crop_30_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.8625869154930115</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay:0.86, haohao_hanhtim:0.85, haohao_mixao_haisan:0.83, haohao_prem_tomchuacay:0.81, haohao_mixao_tomchuangot:0.81</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Comparing the cropped shelf image with the candidate references, the packaging features the distinct pink background, the brand name 'Hảo Hảo', and the specific label 'MÌ TÔM CHUA CAY', which matches the standard Hảo Hảo Tôm Chua Cay design (haohao_tomchuacay). Other options like Premium or other flavors do not match the visible text and layout.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>crop_31_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.7793623805046082</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.78, haohao_mixao_tomchuangot:0.78, haohao_hanhtim:0.77, haohao_tomchuacay:0.76, haohao_mixao_haisan:0.76</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>The query image shows a Hảo Hảo packaging with green background and the text "RAU NẤM". Comparing it with the candidates, the closest match is "haohao_chay" (Mì Hảo Hảo chay rau nấm). The distinct green background and "RAU NẤM" label uniquely confirm this candidate.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>crop_32_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>haohao_prem_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.8485885262489319</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>haohao_prem_tomchuacay:0.85, haohao_prem_bosate:0.84, haohao_hanhtim:0.83, haohao_tomchuacay:0.81, haohao_mixao_haisan:0.81</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>The crop image displays the packaging of 'Hảo Hảo Premium' with the text 'HƯƠNG VỊ MÌ TÔM CHUA CAY' and 'Gói súp lớn', which matches the reference image for 'haohao_prem_tomchuacay'. Other candidates like 'haohao_prem_bosate' feature beef saté instead of shrimp and sour flavor. Therefore, the confirmed product is haohao_prem_tomchuacay.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>crop_33_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.8496281504631042</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate:0.85, haohao_hanhtim:0.82, haohao_mixao_haisan:0.81, haohao_prem_tomchuacay:0.80, haohao_tomchuacay:0.80</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Comparing the query crop against the reference images, the packaging features the distinct 'Hảo Hảo' brand logo, the 'PREMIUM' banner, and the text 'TRỘN BÒ SA TẾ' with an image of sliced beef on the right side. This matches the 'haohao_prem_bosate' reference image precisely, ruling out all other options.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>crop_34_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.8677406311035156</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate:0.87, haohao_hanhtim:0.84, haohao_prem_tomchuacay:0.83, haohao_mixao_haisan:0.81, denhat_thitbam:0.80</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>The query image displays the text "PREMIUM" underneath the Hảo Hảo logo, along with "MÌ TRỘN BÒ SA TẾ" and "Gói súp lớn đậm đà". Comparing this with the candidates, it matches the packaging of haohao_prem_bosate exactly.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>crop_35_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.643917977809906</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>denhat_thitbam:0.65, haohao_chay:0.64, haohao_prem_tomchuacay:0.63, milo_org_180:0.62, haohao_handy_tomchuacay:0.61</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The crop displays the text "hương vị RAU NẤM" along with the distinct Hảo Hảo branding font ("Hảo Hảo vị sự...") and mushroom imagery on a green background. Comparing this to the candidates, it matches the packaging of 'Mì Hảo Hảo chay rau nấm 74g' (haohao_chay).</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>crop_36_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>koreno_volcano</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.8828089833259583</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>koreno_volcano:0.88, koreno_prem_kimchi:0.73, samyang_org_140:0.71, samyang_chacharoni_140:0.70, haohao_mixao_haisan:0.69</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>The crop clearly displays the words "VOLCANO" and "Mì xào KORENO" along with the character design and flavor text "Vị gà phô mai", perfectly matching the reference image for koreno_volcano.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>crop_37_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>omachi_spa_goi</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.8418747186660767</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>omachi_spa_goi:0.84, omachi_tomchuacay_goi:0.76, omachi_suonham_goi:0.75, denhat_thitbam:0.70, denhat_photron_cay_goi:0.68</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Comparing the crop to the candidates, the package clearly shows the 'Omachi' brand and 'Xốt Spaghetti' with the text 'XỐT BÒ BẦM CÀ CHUA' and 'THÊM GÓI PHÔ MAI', matching the reference image for 'omachi_spa_goi' (Mì trộn Omachi xốt Spaghetti 90g) almost exactly.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>crop_38_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>haohao_mixao_tomchuangot</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.7933046221733093</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>haohao_mixao_tomchuangot:0.79, haohao_mixao_haisan:0.76, haohao_chay:0.75, haohao_hanhtim:0.72, haohao_prem_bosate:0.71</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Comparing the crop image to the candidate products, we see the text "Mì Xào" in blue and green background with the label "Hảo Hảo hương vị Tôm Xào Chua Ngọt" matching the product haohao_mixao_tomchuangot. The distinct green background, blue typography for "Mì Xào", and layout completely match the reference image for haohao_mixao_tomchuangot.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>crop_39_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>haohao_mixao_haisan</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.8676639795303345</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>haohao_mixao_haisan:0.87, haohao_hanhtim:0.83, haohao_mixao_tomchuangot:0.83, haohao_tomchuacay:0.79, denhat_thitbam:0.78</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>The target crop displays the text 'Mì Xào' underneath the 'Hảo Hảo' brand, alongside 'hướng vị HẢI SẢN', matching the packaging design of the 'haohao_mixao_haisan' reference image. This rules out other non-mix flavors and other candidates like haohao_mixao_tomchuangot.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>crop_40_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8061712384223938</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.81, haohao_mixao_haisan:0.76, haohao_hanhtim:0.75, haohao_mixao_tomchuangot:0.75, haohao_prem_tomchuacay:0.74</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against all reference options, the green background color matches the Hảo Hảo chay rau nấm packaging. The distinct text and visual design on the crop directly correspond to the 'haohao_chay' reference image.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>crop_41_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>haohao_hanhtim</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8604266047477722</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>haohao_hanhtim:0.86, haohao_mixao_haisan:0.79, haohao_prem_bosate:0.76, haohao_prem_tomchuacay:0.75, haohao_tomchuacay:0.75</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>The product packaging clearly displays the text "SA TẾ HÀNH TÍM" underneath the Hảo Hảo logo, and the background color is purple, matching the reference image for haohao_hanhtim (Mì Hảo Hảo sa tế hành tím gói 75g).</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>crop_42_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.803216278553009</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.80, haohao_mixao_haisan:0.76, haohao_hanhtim:0.74, haohao_mixao_tomchuangot:0.74, haohao_tomchuacay:0.72</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The query image shows a green packaging with the Hảo Hảo logo and text matching the vegetarian variant ('Mì Chay' / 'hương vị rau nấm'). Comparing it with the candidates, it clearly matches the green packaging of 'haohao_chay' (Mì Hảo Hảo chay rau nấm 74g).</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>crop_43_ok.jpg</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.4996480047702789</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>oreo_vanil_105:0.50, pepsi_org_lon_320:0.48, pepsi_org_chai_600:0.47, coca_zero_chai_390:0.47, coca_zero_chai_600:0.46</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>The provided crop shows the word 'Omachi' in a distinctive font and color, along with Vietnamese text such as 'Mì khoai tây' on the packaging. None of the reference options (which include Oreo, Pepsi, and Coca-Cola Zero products) match the Omachi brand or product name. Therefore, none of the candidates are correct.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>crop_file</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>predicted_sku_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>top5_candidates</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>llm_reasoning</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>true_sku_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>crop_00_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>otoki_cheese_cay</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7607427835464478</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>otoki_cheese:0.76, otoki_cheese_cay:0.76, samyang_org_140:0.72, denhat_thitbam:0.71, siukay_gaphomai_goi:0.71</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The query crop displays the text 'VỊ PHÔ MAI CHEDDAR CAY' on a black packaging background with yellow 'CHEESY' lettering, which matches the packaging design of 'otoki_cheese_cay'. Other options like 'otoki_cheese' have a yellow background, and 'siukay_gaphomai_goi' has a different text layout and bright yellow border. Therefore, the confirmed product is 'otoki_cheese_cay'.</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>crop_01_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>otoki_cheese</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8444159626960754</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>otoki_cheese:0.84, otoki_cheese_cay:0.79, siukay_gaphomai_goi:0.73, denhat_thitbam:0.72, indomie_dacbiet:0.72</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The product packaging features a yellow background with large 'CHEESY' and 'RAMEN' text, along with a white speech bubble showing 'VỊ PHÔ MAI CHEDDAR' and a bowl of noodles topped with a fried egg. Comparing this to the reference images, it matches the packaging of 'otoki_cheese' (Mì phô mai cheddar Otoki 110g) perfectly in layout, text, and design.</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>crop_02_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>samyang_cheese_140</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8778430819511414</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>samyang_cheese_140:0.88, samyang_org_140:0.85, samyang_cream_carbonara_140:0.81, samyang_chacharoni_140:0.81, otoki_cheese:0.77</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The crop displays the characteristic yellow packaging, the Samyang Buldak chicken mascot eating a piece of cheese on top of a wheel of cheese, and the word 'Cheese' next to the Korean text '치즈 불닭볶음면'. This matches the reference image for 'samyang_cheese_140' perfectly.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>crop_03_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>samyang_org_140</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8615518808364868</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>samyang_org_140:0.86, samyang_chacharoni_140:0.79, samyang_cream_carbonara_140:0.78, samyang_cheese_140:0.78, chapagetti_goi_137:0.76</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The crop image shows a black packaging with the red Korean text '불닭볶음면' and the classic Samyang Buldak chicken mascot, which matches the original flavour variant samyang_org_140. Comparing it against samyang_chacharoni_140, samyang_cream_carbonara_140, and samyang_cheese_140, the background color is black instead of brown, pink, or yellow, and there are no extra flavor icons like cream or cheese, perfectly matching the original version.</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>crop_04_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>samyang_cream_carbonara_140</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8539941310882568</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>samyang_cream_carbonara_140:0.85, samyang_org_140:0.76, samyang_cheese_140:0.75, samyang_chacharoni_140:0.70, siukay_bo_goi:0.68</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the reference candidates, the packaging clearly displays 'Buldak' and 'Cream Carbonara' along with the iconic character and pink-and-light-green color theme matching samyang_cream_carbonara_140.</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>crop_05_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>samyang_org_140</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5722783207893372</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>samyang_org_140:0.57, samyang_cream_carbonara_140:0.56, maeil_nho:0.51, samyang_cheese_140:0.50, maeil_tao:0.49</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The cropped image shows the character Hochi holding a small cup or bowl with a spoon, wearing a green skirt with yellow polka dots, which matches the artwork on the classic black packaging of 'samyang_org_140' (Mì Samyang Buldak Gà Cay Khô Vị Truyền Thống 140g). Other candidates such as cream carbonara or cheese feature different background colors and clothing designs on the character.</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>crop_06_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8309429883956909</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi:0.83, samyang_chacharoni_140:0.73, samyang_org_140:0.72, shin_org_goi_120:0.72, haohao_prem_bosate:0.72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The query image displays the yellow 'KORENO' brand name and the word 'PREMIUM' in a specific font and layout characteristic of the Koreno noodle packaging. Comparing it against the reference options, it matches the orange-red packaging and distinctive branding of 'koreno_prem_kimchi'.</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>crop_07_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>shin_org_goi_120</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7772074341773987</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>shin_org_goi_120:0.78, samyang_org_140:0.71, samyang_chacharoni_140:0.70, chapagetti_goi_137:0.69, jin_jjajang_goi_135:0.66</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>The product packaging features the prominent black character '辛', the text 'SHIN RAMYUN', and the face of an idol on the right side. Comparing it with the reference images, it matches the Shin Ramyun Nongshim packet (shin_org_goi_120).</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>crop_08_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8556005358695984</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi:0.86, haohao_prem_bosate:0.73, haohao_hanhtim:0.73, indomie_dacbiet:0.73, denhat_thitbam:0.73</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The product packaging clearly displays the large yellow text 'KORENO' with the label 'MÌ VỊ KIM CHI' at the bottom left, matching the reference image for 'koreno_prem_kimchi'.</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>crop_09_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>otoki_yeul_kimchi_goi_100</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8958897590637207</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>otoki_yeul_kimchi_goi_100:0.90, nissin_gaccay:0.71, samyang_org_140:0.70, siukay_bo_goi:0.70, shin_org_goi_120:0.70</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The user image clearly shows a black packaging with the brand logo 'OTOKI' at the top left, and the text 'MÌ YEUL' along with 'KIMCHI CAY' in bold yellow lettering, which matches the reference image for 'otoki_yeul_kimchi_goi_100'.</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>crop_10_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8916890621185303</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135:0.89, samyang_chacharoni_140:0.76, samyang_org_140:0.74, chapagetti_goi_137:0.74, shin_org_goi_120:0.74</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>The product packaging features a bright yellow background, the Ottogi logo ('OTOKI'), and the bold text 'Jin jjajang', perfectly matching the reference image for 'jin_jjajang_goi_135'.</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>crop_11_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>samyang_chacharoni_140</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.8551577925682068</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>samyang_chacharoni_140:0.86, samyang_org_140:0.80, jin_jjajang_goi_135:0.77, shin_org_goi_120:0.76, chapagetti_goi_137:0.74</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the reference candidates, the packaging features the distinct dark brown background, the prominent golden 'Olive Oil' label on the right side, and the Korean text '짜짜로니' at the bottom. This matches the Samyang Chacharoni 140g packaging (samyang_chacharoni_140) perfectly.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>crop_12_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8687357306480408</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>jin_jjajang_goi_135:0.87, samyang_chacharoni_140:0.72, denhat_thitbam:0.72, indomie_dacbiet:0.70, samyang_org_140:0.70</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>The image clearly shows the prominent text "Jin jjajang" and "Mì xốt tương đen" matching the packaging of the Jin Jjajang xốt tương đen Ottogi 135g product reference image, while ruling out other instant noodle variants.</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>crop_13_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>koreno_prem_kimchi</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7289931178092957</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>denhat_thitbam:0.77, indomie_dacbiet:0.73, koreno_prem_kimchi:0.73, samyang_chacharoni_140:0.72, samyang_org_140:0.71</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Comparing the crop image to the candidate products, the packaging prominently displays 'MÌ VỊ KIM CHI' and shows an orange-red background with a bowl of noodle soup featuring a distinct piece of kimchi, which matches the design of the Koreno Premium Kimchi instant noodle package ('koreno_prem_kimchi'). Other options like Samyang or Indomie have entirely different brand styles and graphics. Therefore, the product is identified as koreno_prem_kimchi.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>crop_14_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>koreno_volcano</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6655938625335693</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.69, nissin_gaccay:0.68, denhat_thitbam:0.67, siukay_bo_goi:0.67, koreno_volcano:0.67</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Comparing the crop image to the candidate products, we see the text "CAY" in yellow with a red outline at the top and black background matching the Koreno Volcano packaging design style. Specifically, looking closely at the Koreno Volcano reference image, it features the prominent text "CÂY" (with flame background style) matching the visual elements. However, let's check other candidates: none of the others match the black packaging with the specific red/yellow CAY text layout. Wait, let's look at koreno_volcano: it has the black wrapper and the text style matches, but let's compare with the other options. The typography and dark packaging design confirm it is koreno_volcano.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>crop_15_ok.jpg</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7200273871421814</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.72, samyang_org_140:0.72, denhat_photron_cay_goi:0.71, denhat_photron_bo_goi:0.71, denhat_thitbam:0.70</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>The crop displays a packaging with the prominent text 'THẦN ỚT' and an angry red chili character blowing fire, which does not match any of the provided candidate products (siukay_gaphomai_goi, samyang_org_140, denhat_photron_cay_goi, denhat_photron_bo_goi, denhat_thitbam). Therefore, the correct classification is unknown.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>crop_16_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>siukay_haisan_goi</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8281581401824951</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.84, siukay_haisan_goi:0.83, siukay_bo_goi:0.78, nissin_gaccay:0.69, haohao_prem_bosate:0.68</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The image shows a black-packaged instant noodle with the prominent yellow logo 'SiuKay' and text reading 'Hương vị Hải Sản' (Seafood flavour) on the bottom left corner. Comparing this to the reference candidates, it matches the packaging of 'siukay_haisan_goi'.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>crop_17_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8477725386619568</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137:0.85, samyang_chacharoni_140:0.78, samyang_org_140:0.73, jin_jjajang_goi_135:0.71, shin_org_goi_120:0.69</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Comparing the user's cropped shelf image with the plausible candidates, the packaging clearly shows the large white text 'Chapagetti' at the top, combined with a red-and-black background and a 'SPICY' logo on the left featuring chili peppers. This matches the exact visual features of 'chapagetti_goi_137' (Mì trộn tương đen cay Nongshim Chapagetti gói 137g).</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>crop_18_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>siukay_bo_goi</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8480976223945618</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>siukay_bo_goi:0.85, siukay_gaphomai_goi:0.84, siukay_haisan_goi:0.82, samyang_org_140:0.74, nissin_gaccay:0.73</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>The query image displays the distinct large yellow font 'SiuKay' with a red chili accent replacing the 'i', along with the Acecook logo and 'Hương vị Bò' (Beef flavor) text on the left, matching the reference image for siukay_bo_goi precisely.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>crop_19_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8781773447990417</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>siukay_gaphomai_goi:0.88, siukay_haisan_goi:0.78, siukay_bo_goi:0.76, samyang_cream_carbonara_140:0.70, nissin_gaccay:0.70</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>The crop image clearly displays the 'SiuKay' brand logo in yellow with a red chili replacing the 'i', along with the Acecook logo and the text 'GÀ XỐT PHÔ MAI'. This matches the reference image for 'siukay_gaphomai_goi' perfectly in all design details, typography, and flavor text.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>crop_20_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.8182909488677979</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>chapagetti_goi_137:0.82, samyang_chacharoni_140:0.79, samyang_org_140:0.77, jin_jjajang_goi_135:0.73, siukay_haisan_goi:0.71</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>The product image clearly displays the Korean text '매콤한 사천 짜파게티' and the English text 'Korean black spaghetti with roasted chajang sauce' with a 'SPICY' chili badge, which matches the Nongshim Chapagetti Spicy 137g packaging (chapagetti_goi_137). Other options like Samyang or Ottogi are ruled out immediately by brand and packaging details.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>crop_21_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>indomie_caynong</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6919452548027039</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.70, indomie_caynong:0.69, denhat_thitbam:0.68, denhat_photron_bo_goi:0.65, jin_jjajang_goi_135:0.64</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>The query image clearly shows the packaging for 'Mì goreng Pedas' with the text 'vị cay nồng' and 'Mì xào khô'. Comparing it with the reference images, it matches the Indomie Mì xào cay nồng Indomie gói 79g (indomie_caynong) packaging design and text layout precisely, while being distinct from the other Indomie variety ('indomie_dacbiet').</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>crop_22_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>indomie_caynong</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.670721709728241</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>indomie_caynong:0.67, indomie_dacbiet:0.66, denhat_thitbam:0.65, samyang_org_140:0.63, samyang_cream_carbonara_140:0.63</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against the reference candidates, we can see the distinctive Indomie logo with blue text, yellow stripe, and green stripe on the right side of the packaging. The visible text reads 'Mi goreng Pedas' and 'stant Noodles', perfectly matching the 'indomie_caynong' packaging layout and design, confirming the final answer.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>crop_23_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8253313302993774</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.83, denhat_thitbam:0.78, indomie_caynong:0.78, indomie_hypeabis:0.74, koreno_prem_kimchi:0.72</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Comparing the cropped image against the plausible candidates, the packaging clearly shows the Indomie logo and the text 'Mi Goreng' with 'Vị đặc biệt'. This perfectly matches the reference image for 'indomie_dacbiet', ruling out other variants like 'indomie_caynong' or 'indomie_hypeabis'.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>crop_24_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.809359610080719</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.81, indomie_caynong:0.80, denhat_thitbam:0.77, indomie_hypeabis:0.75, koreno_prem_kimchi:0.69</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against the reference candidates, the packaging clearly shows the blue 'Indomie' logo, red background top with green banner, and 'Mi Goreng' text matching Indomie noodles. Specifically, looking at the text below 'Mi Goreng', it matches the special variant 'indomie_dacbiet' (Mì xào khô đặc biệt) featuring the white/red layout with visible letters 'đặc biệt' style text.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>crop_25_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nissin_gaccay</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8427699208259583</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>nissin_gaccay:0.84, siukay_gaphomai_goi:0.75, siukay_bo_goi:0.74, siukay_haisan_goi:0.73, indomie_dacbiet:0.72</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the reference candidates, the packaging clearly displays the brand name 'NISSIN' alongside the text 'GÀ CAY PHÔ MAI', matching the 'nissin_gaccay' (Mì xào Nissin gà cay phô mai Hàn Quốc 72g) reference image perfectly.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>crop_26_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.8060095310211182</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.81, indomie_caynong:0.75, denhat_thitbam:0.75, indomie_hypeabis:0.73, haohao_mixao_haisan:0.70</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Comparing the shelf crop to the candidate reference images, the packaging clearly shows the blue and red Indomie logo and the text 'Mi Goreng' with 'Mì xào khô Vị đặc biệt'. This matches the reference image for 'indomie_dacbiet' perfectly in terms of background design, font, and flavor text.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>crop_27_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.8246777653694153</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>indomie_dacbiet:0.82, denhat_thitbam:0.78, indomie_caynong:0.77, indomie_hypeabis:0.74, haohao_mixao_haisan:0.72</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against the reference candidates, the packaging clearly displays the blue 'Indomie' logo, 'Instant Noodles', and the 'Mi Goreng' text characteristic of the Indomie line. Specifically, the top text 'Vị đặc biệt' and packaging features match the 'indomie_dacbiet' reference image.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>crop_28_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7703028321266174</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.77, haohao_mixao_tomchuangot:0.75, denhat_thitbam:0.74, haohao_hanhtim:0.73, haohao_tomchuacay:0.73</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>The query image clearly shows the 'Hảo Hảo' brand logo above the text 'Mì Chay' with a green background featuring leaf illustrations. Comparing this packaging design and the visible text to the reference images, it matches the 'haohao_chay' (Mì Hảo Hảo chay rau nấm) product exactly, ruling out the other candidates which have different flavor text and packaging designs.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>crop_29_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.8351150751113892</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay:0.84, haohao_hanhtim:0.81, haohao_prem_tomchuacay:0.81, haohao_mixao_haisan:0.80, haohao_chay:0.78</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>The product packaging has a pink color background and clearly displays the text "MÌ TÔM CHUA CAY" matching the standard Hảo Hảo Tôm Chua Cay variant. Comparing it with the reference images, the logo style and text layout perfectly match haohao_tomchuacay.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>crop_30_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.8625869154930115</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>haohao_tomchuacay:0.86, haohao_hanhtim:0.85, haohao_mixao_haisan:0.83, haohao_prem_tomchuacay:0.81, haohao_mixao_tomchuangot:0.81</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Comparing the crop image with the reference candidates, the packaging features the classic pink color scheme, the red 'Hảo Hảo' logo, and the text 'MÌ TÔM CHUA CAY' corresponding to the standard Mì Hảo Hảo vị tôm chua cay. This matches the 'haohao_tomchuacay' reference image rather than the Premium version or other flavors.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>crop_31_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.7793623805046082</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.78, haohao_mixao_tomchuangot:0.78, haohao_hanhtim:0.77, haohao_tomchuacay:0.76, haohao_mixao_haisan:0.76</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>The crop image shows a green packaging with the text 'Mì Chay' and 'HƯƠNG VỊ RAU NẤM'. Comparing it to the candidates, it matches the exact green design and flavor text of 'haohao_chay' (Mì Hảo Hảo chay rau nấm).</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>crop_32_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>haohao_prem_tomchuacay</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.8485885262489319</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>haohao_prem_tomchuacay:0.85, haohao_prem_bosate:0.84, haohao_hanhtim:0.83, haohao_tomchuacay:0.81, haohao_mixao_haisan:0.81</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>The product packaging clearly displays the word 'PREMIUM' beneath the 'Hảo Hảo' logo and the text 'MÌ TÔM CHUA CAY' with 'Gói súp lớn đậm đà nâng tầm Hảo vị', matching the packaging of 'haohao_prem_tomchuacay'. Other options like regular Hảo Hảo or Hảo Hảo Premium bò sa tế are ruled out based on the flavor name and visual elements.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>crop_33_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.8496281504631042</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate:0.85, haohao_hanhtim:0.82, haohao_mixao_haisan:0.81, haohao_prem_tomchuacay:0.80, haohao_tomchuacay:0.80</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Comparing the query image with the candidates, the packaging shows the 'Hảo Hảo' brand and 'PREMIUM' text clearly, along with the label 'MÌ TRỘN BÒ SA TẾ'. This matches the 'haohao_prem_bosate' reference image featuring beef slices and dark/yellow premium packaging.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>crop_34_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.8677406311035156</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>haohao_prem_bosate:0.87, haohao_hanhtim:0.84, haohao_prem_tomchuacay:0.83, haohao_mixao_haisan:0.81, denhat_thitbam:0.80</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>The query image displays the golden packaging of 'Hảo Hảo' with the text 'PREMIUM', and specifically shows the label 'MÌ TRỘN BÒ SA TẾ' alongside a depiction of beef slices. Comparing this to the candidates, it matches exactly with 'haohao_prem_bosate' (Mì trộn Hảo Hảo Premium hương vị bò sa tế).</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>crop_35_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.643917977809906</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>denhat_thitbam:0.65, haohao_chay:0.64, haohao_prem_tomchuacay:0.63, milo_org_180:0.62, haohao_handy_tomchuacay:0.61</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The crop shows the text 'hương vị RAU NẤM' along with a green background and mushroom illustrations. Comparing this with the candidates, 'haohao_chay' matches the text 'hương vị RAU NẤM' and the characteristic green-and-red Hảo Hảo design for the vegetarian line. Therefore, the product is Mì Hảo Hảo chay rau nấm.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>crop_36_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>koreno_volcano</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.8828089833259583</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>koreno_volcano:0.88, koreno_prem_kimchi:0.73, samyang_org_140:0.71, samyang_chacharoni_140:0.70, haohao_mixao_haisan:0.69</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>The crop clearly displays the words "VOLCANO", "Mì xào KORENO", and "Vị gà phomai" along with the distinct cartoon chicken graphic characteristic of the Koreno Volcano product. Comparing it against the provided reference images, it matches the packaging of 'koreno_volcano' precisely.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>crop_37_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>omachi_spa_goi</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.8418747186660767</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>omachi_spa_goi:0.84, omachi_tomchuacay_goi:0.76, omachi_suonham_goi:0.75, denhat_thitbam:0.70, denhat_photron_cay_goi:0.68</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>The image clearly shows the Omachi logo at the top with the text 'Xốt Spaghetti' underneath, and features a green background with a picture of spaghetti and minced meat with tomato sauce ('XỐT BÒ BẰM CÀ CHUA', 'THÊM GÓI PHÔ MAI'). This matches the packaging design of 'omachi_spa_goi' perfectly.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>crop_38_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>haohao_mixao_tomchuangot</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.7933046221733093</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>haohao_mixao_tomchuangot:0.79, haohao_mixao_haisan:0.76, haohao_chay:0.75, haohao_hanhtim:0.72, haohao_prem_bosate:0.71</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Comparing the crop image to the available candidates, the package clearly shows the large blue text 'Mi Xào' and the green background color, which matches the Mì xào Hảo Hảo tôm chua ngọt packaging. Specifically, the visible text 'hướng vị Tôm Xào' confirms it is haohao_mixao_tomchuangot.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>crop_39_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>haohao_mixao_haisan</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.8676639795303345</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>haohao_mixao_haisan:0.87, haohao_hanhtim:0.83, haohao_mixao_tomchuangot:0.83, haohao_tomchuacay:0.79, denhat_thitbam:0.78</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>The query image clearly displays the text "Mì Xào" under the brand "Hảo Hảo" and the flavor label "hương vị HẢI SẢN". Comparing this against the plausible candidates, it perfectly matches the packaging design of "haohao_mixao_haisan" (Mì xào Hảo Hảo hải sản 75g), featuring the signature red background, white/black text layout, and scallop illustration.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>crop_40_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8061712384223938</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.81, haohao_mixao_haisan:0.76, haohao_hanhtim:0.75, haohao_mixao_tomchuangot:0.75, haohao_prem_tomchuacay:0.74</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against all candidates, the packaging has a green background with the text 'Hảo Hảo' and 'Mì Chay' clearly visible at the bottom. This matches the 'haohao_chay' reference image which shows the green packaging and the text 'Mì Chay' with 'hương vị RAU NẤM'. All other candidates have different colors or flavor titles, confirming 'haohao_chay' as the correct match.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>crop_41_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>haohao_hanhtim</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.8604266047477722</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>haohao_hanhtim:0.86, haohao_mixao_haisan:0.79, haohao_prem_bosate:0.76, haohao_prem_tomchuacay:0.75, haohao_tomchuacay:0.75</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Comparing the crop image against the reference images, the packaging displays the purple background and the text "SA TẾ HÀNH TÍM", which matches the haohao_hanhtim SKU (Mì Hảo Hảo sa tế hành tím gói 75g). The text and layout precisely align with the reference image for haohao_hanhtim.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>crop_42_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>haohao_chay</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.803216278553009</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>haohao_chay:0.80, haohao_mixao_haisan:0.76, haohao_hanhtim:0.74, haohao_mixao_tomchuangot:0.74, haohao_tomchuacay:0.72</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The cropped image shows a green packaging with the signature 'Hảo Hảo' logo and the text 'Mì Chay', which matches the reference image for 'haohao_chay' (Mì Hảo Hảo chay rau nấm). Other green packages like 'haohao_mixao_tomchuangot' have entirely different text layout ('Mì Xào'). Therefore, the correct product is 'haohao_chay'.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>crop_43_ok.jpg</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.4996480047702789</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>oreo_vanil_105:0.50, pepsi_org_lon_320:0.48, pepsi_org_chai_600:0.47, coca_zero_chai_390:0.47, coca_zero_chai_600:0.46</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>The provided crop shows the brand name 'Omachi' in a distinctive red and white font, and Vietnamese text mentioning 'mì khoai tây'. None of the reference options (which are Oreo cookies, Pepsi, and Coca-Cola Zero beverages) match this brand or product category. Therefore, the product cannot be matched to any of the valid candidates, making 'unknown' the correct answer.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>crop_file</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>predicted_sku_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>top5_candidates</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>llm_reasoning</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>true_sku_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>crop_00_ok.jpg</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>samyang_cream_carbonara_140</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8831787109375</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>samyang_cream_carbonara_140:0.88, samyang_org_140:0.81, samyang_cheese_140:0.78, samyang_chacharoni_140:0.72, siukay_bo_goi:0.70</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The packaging features the distinct pink and yellow design, with the text 'Buldak Cream Carbonara' and the mascot Hochi characteristic of the Samyang Buldak Cream Carbonara 140g variant. This matches the reference image for samyang_cream_carbonara_140 precisely.</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
@@ -9476,20 +14220,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>samyang_cheese_140</t>
+          <t>samyang_org_140</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8773151040077209</v>
+        <v>0.7784572243690491</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>samyang_cheese_140:0.88, samyang_org_140:0.84, samyang_cream_carbonara_140:0.80, samyang_chacharoni_140:0.79, otoki_cheese:0.75</t>
+          <t>samyang_org_140:0.78, samyang_chacharoni_140:0.70, samyang_cream_carbonara_140:0.70, siukay_bo_goi:0.70, indomie_dacbiet:0.69</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The crop image matches the 'samyang_cheese_140' reference image perfectly. The key identifying features are the character (the chicken) eating a piece of yellow cheese, the yellow packaging background, the specific stylized 'Cheese' text, and the Korean text '치즈 불닭볶음면'. These elements align exactly with the Samyang Buldak Cheese 140g packaging.</t>
+          <t>The crop displays the iconic black packaging of Samyang Buldak with the angry chicken character and the frying pan illustration containing red noodles, which matches the original Buldak flavor (samyang_org_140) perfectly.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -9509,20 +14253,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>otoki_cheese</t>
+          <t>samyang_cheese_140</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8150874376296997</v>
+        <v>0.8817604780197144</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>otoki_cheese:0.82, otoki_cheese_cay:0.77, indomie_dacbiet:0.72, nissin_gaccay:0.72, siukay_gaphomai_goi:0.71</t>
+          <t>samyang_cheese_140:0.88, samyang_org_140:0.85, samyang_cream_carbonara_140:0.80, samyang_chacharoni_140:0.79, otoki_cheese:0.77</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The crop shows packaging with the text 'OTOKI' and 'CHEESY', and clearly features the text 'VỊ PHÔ MAI CHEDDAR'. Comparing this to the reference images, it matches the Otoki Cheesy Ramen ('otoki_cheese') packaging perfectly. Other candidates are easily ruled out by brand name and package design differences.</t>
+          <t>The product packaging features a yellow background with the iconic Samyang Buldak chicken character eating a slice of cheese, sitting on a cheese wheel, and the Korean text "치즈 불닭볶음면" along with the English "Cheese" logo. This matches the reference image for samyang_cheese_140 perfectly.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -9542,20 +14286,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>otoki_cheese_cay</t>
+          <t>otoki_cheese</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8847552537918091</v>
+        <v>0.7982364296913147</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>otoki_cheese_cay:0.88, otoki_cheese:0.82, denhat_thitbam:0.75, nissin_gaccay:0.75, koreno_prem_kimchi:0.75</t>
+          <t>otoki_cheese:0.80, otoki_cheese_cay:0.76, nissin_gaccay:0.73, siukay_gaphomai_goi:0.73, siukay_bo_goi:0.70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The crop shows a black packaging with the brand 'OTOKI' and the text 'MÌ TRỘN CHEESY' and 'VỊ PHÔ MAI CHEDDAR CAY'. This matches the reference image for 'otoki_cheese_cay' exactly.</t>
+          <t>The crop displays a yellow packaging with the brand logo "Otoki" at the top left and large text "CHEESY" and "RAMEN", along with the label "VỊ PHÔ MAI CHEDDAR". This matches the reference image for "otoki_cheese" (Mì phô mai cheddar Otoki 110g) completely in packaging design, text, and flavor description.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -9575,20 +14319,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>samyang_org_140</t>
+          <t>otoki_cheese_cay</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.857998251914978</v>
+        <v>0.8643540740013123</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>samyang_org_140:0.86, samyang_cream_carbonara_140:0.79, samyang_cheese_140:0.77, samyang_chacharoni_140:0.77, shin_org_goi_120:0.75</t>
+          <t>otoki_cheese_cay:0.86, otoki_cheese:0.79, nissin_gaccay:0.75, siukay_gaphomai_goi:0.73, koreno_prem_kimchi:0.72</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The crop displays the iconic black packaging of the Samyang Buldak Hot Chicken Flavor Ramen (original). It features the distinct 'angry' character with a spiral on its cheek, the fire-breathing animation, and the overall design matches the samyang_org_140 reference image exactly.</t>
+          <t>The product packaging shown in the query image features the 'OTOKI' brand logo at the top left, the bold text 'MÌ TRỘN CHEESY', and the label 'VỊ PHÔ MAI CHEDDAR CAY' on the front, which matches the reference image for 'otoki_cheese_cay' (Mì trộn vị phô mai cheddar cay Otoki 120g). Other candidates like 'otoki_cheese' or 'nissin_gaccay' can be ruled out due to different text and packaging color/design.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -9608,20 +14352,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dalatmilk_less_180</t>
+          <t>samyang_org_140</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6226761937141418</v>
+        <v>0.8788632154464722</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dalatmilk_less_180:0.62, th_probiotic_org_85:0.60, pepsi_org_lon_320:0.60, aquafina_5l:0.59, lavie_org_chai_1l5:0.57</t>
+          <t>samyang_org_140:0.88, samyang_chacharoni_140:0.80, samyang_cream_carbonara_140:0.78, shin_org_goi_120:0.77, samyang_cheese_140:0.77</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The crop displays a stack of product packaging with a blue and white design featuring the Dalat Milk brand. The partial text and specific graphical layout of the cow and landscape on the packaging matches the reference image for the 180ml Dalat Milk Less Sugar product.</t>
+          <t>The image shows a black packaging with the iconic Samyang Buldak chicken character breathing fire, matching the design of samyang_org_140. Comparing it against samyang_cream_carbonara_140 (pink packaging), samyang_cheese_140 (yellow packaging), samyang_chacharoni_140 (maroon packaging), and shin_org_goi_120 (red packaging with Shin character), the black background and fiery chicken illustration confirm it is the original Buldak flavor.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -9641,20 +14385,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>th_probiotic_org_85</t>
+          <t>otoki_yeul_kimchi_goi_100</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5399167537689209</v>
+        <v>0.7866488695144653</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>aquafina_5l:0.58, lavie_org_chai_1l5:0.56, dalatmilk_less_180:0.55, pepsi_org_lon_320:0.55, th_probiotic_org_85:0.54</t>
+          <t>otoki_yeul_kimchi_goi_100:0.79, samyang_org_140:0.68, siukay_bo_goi:0.66, siukay_haisan_goi:0.65, koreno_volcano:0.65</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The crop shows a blurry image, but the distinct silhouette and structural design of the product in the center clearly match the bottle shape of the 'th_probiotic_org_85' (TH True Yogurt Probi 85ml). The white color and the specific curvature of the top and bottom of the bottle in the crop are characteristic of this product.</t>
+          <t>Comparing the crop image against the candidates, the package clearly shows the 'OTOKI' brand logo at the top left and the text 'MÌ YEUL' alongside the distinctive Korean lettering and flame design. This matches the reference image for 'otoki_yeul_kimchi_goi_100' exactly, ruling out all other options.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -9678,16 +14422,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8731816411018372</v>
+        <v>0.8712349534034729</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>samyang_chacharoni_140:0.87, samyang_org_140:0.84, shin_org_goi_120:0.81, jin_jjajang_goi_135:0.80, chapagetti_goi_137:0.78</t>
+          <t>samyang_chacharoni_140:0.87, samyang_org_140:0.82, jin_jjajang_goi_135:0.80, shin_org_goi_120:0.78, chapagetti_goi_137:0.77</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The product in the crop image is 'Samyang Chacharoni' based on the prominent, bold Korean text '짜짜로니' (Chacharoni) and the golden olive oil seal graphic on the right side. This matches the 'samyang_chacharoni_140' reference image perfectly in design, brand, and layout.</t>
+          <t>The product packaging features the distinctive 'Olive Oil' emblem on the upper right and Korean text '짜짜로니' on the bottom, which matches the design of the Samyang Chacharoni 140g reference image (samyang_chacharoni_140) perfectly and excludes all other options.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -9711,16 +14455,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8982495665550232</v>
+        <v>0.8961634039878845</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>jin_jjajang_goi_135:0.90, samyang_chacharoni_140:0.77, samyang_org_140:0.76, shin_org_goi_120:0.75, chapagetti_goi_137:0.74</t>
+          <t>jin_jjajang_goi_135:0.90, samyang_chacharoni_140:0.76, chapagetti_goi_137:0.74, samyang_org_140:0.73, shin_org_goi_120:0.71</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The crop image clearly displays the Ottogi logo and the text 'Jin jjajang', which matches the 'jin_jjajang_goi_135' reference image exactly in terms of design, branding, and text layout.</t>
+          <t>The product packaging clearly displays the Ottogi logo and the distinctive 'Jin Jjajang' brand name in Korean and English, matching the reference image for 'jin_jjajang_goi_135'.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -9744,16 +14488,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.882205069065094</v>
+        <v>0.8605225086212158</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>otoki_yeul_kimchi_goi_100:0.88, shin_org_goi_120:0.74, samyang_org_140:0.74, nissin_gaccay:0.73, otoki_cheese_cay:0.73</t>
+          <t>otoki_yeul_kimchi_goi_100:0.86, nissin_gaccay:0.70, samyang_org_140:0.70, shin_org_goi_120:0.69, otoki_cheese_cay:0.69</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The crop displays the packaging for 'Mì Yeul Kimchi' by Otoki. Comparing this to the reference images, the design, including the Otoki logo, the text 'REAL KIMCHI CAY' and 'Mi YEUL', matches the 'otoki_yeul_kimchi_goi_100' candidate perfectly.</t>
+          <t>The crop displays a black package with the brand 'OTOKI' and the text 'Mì YEUL KIMCHI CAY'. Comparing this to the reference images, it matches the product 'otoki_yeul_kimchi_goi_100' perfectly in design, brand, and flavor labeling.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -9777,16 +14521,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.89768385887146</v>
+        <v>0.8861693143844604</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>koreno_prem_kimchi:0.90, samyang_org_140:0.78, shin_org_goi_120:0.78, samyang_chacharoni_140:0.77, indomie_dacbiet:0.76</t>
+          <t>koreno_prem_kimchi:0.89, samyang_org_140:0.76, samyang_chacharoni_140:0.76, shin_org_goi_120:0.75, haohao_prem_bosate:0.75</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The crop image clearly displays the brand name 'KORENO' in large yellow text on an orange background, matching the packaging design of the 'koreno_prem_kimchi' reference image. The text 'MÌ VỊ KIM CHI' is also partially visible on the bottom left of the crop, confirming it as the Koreno Premium Kimchi instant noodle product.</t>
+          <t>The product packaging clearly displays the large yellow brand name 'KORENO' over a black background with 'PREMIUM' and Korean text, along with an orange background and a bowl of kimchi noodle soup. This matches the 'koreno_prem_kimchi' reference image perfectly.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -9810,16 +14554,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8101075291633606</v>
+        <v>0.7694615721702576</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>shin_org_goi_120:0.81, samyang_org_140:0.75, samyang_chacharoni_140:0.73, chapagetti_goi_137:0.72, samyang_cream_carbonara_140:0.70</t>
+          <t>shin_org_goi_120:0.77, samyang_org_140:0.72, chapagetti_goi_137:0.69, samyang_chacharoni_140:0.69, jin_jjajang_goi_135:0.66</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The crop displays the distinctive red packaging and the large Chinese character '辛' associated with the Shin Ramyun brand. While it features a promotional image of a person (K-pop idol), which is a common marketing variation for Shin Ramyun, the logo, branding ('SHIN RAMYUN'), and color scheme correspond to the Shin Ramyun product line.</t>
+          <t>Comparing the crop image with the provided candidates, we can clearly see the large black Korean character '辛' on the left and the English text 'SHIN RAMYUN' inside a yellow banner on the right, which uniquely matches the Nongshim Shin Ramyun product (shin_org_goi_120).</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -9839,20 +14583,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pepsi_zero_lon_320</t>
+          <t>chapagetti_goi_137</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.5767812728881836</v>
+        <v>0.8297805190086365</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>oreo_vanil_105:0.63, pepsi_org_lon_320:0.61, pepsi_org_chai_390:0.61, milo_org_180:0.59, pepsi_zero_lon_320:0.58</t>
+          <t>chapagetti_goi_137:0.83, samyang_chacharoni_140:0.77, samyang_org_140:0.73, shin_org_goi_120:0.72, jin_jjajang_goi_135:0.70</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The crop shows a black Pepsi can with the text 'KHÔNG ĐƯỜNG', which matches the reference image for 'pepsi_zero_lon_320'.</t>
+          <t>The crop clearly displays the brand name 'NongSHIM' and the prominent product name 'Chapagetti', along with a red packaging design and 'SPICY' label. Comparing this with the candidates, it matches the Nongshim Chapagetti Spicy 137g packaging precisely ('chapagetti_goi_137').</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -9872,20 +14616,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>coca_org_chai_390</t>
+          <t>siukay_gaphomai_goi</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5072760581970215</v>
+        <v>0.903167724609375</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>pepsi_org_lon_320:0.52, aquafina_5l:0.52, coca_zero_chai_390:0.51, coca_org_chai_390:0.51, pepsi_org_chai_390:0.50</t>
+          <t>siukay_gaphomai_goi:0.90, siukay_haisan_goi:0.81, siukay_bo_goi:0.79, nissin_gaccay:0.71, otoki_cheese_cay:0.70</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The crop shows a vertical red section with text on it, which matches the characteristic side label design of a Coca-Cola product. Comparing this to the Coca-Cola variants provided, the red background and distinct white script styling are consistent with the Coca-Cola original formula branding (coca_org_chai_390).</t>
+          <t>The user image shows a bright yellow packaging with the large text 'SiuKay' and a cartoon chicken holding a chili, matching the reference image for 'siukay_gaphomai_goi'. Comparing against other candidates like 'siukay_bo_goi' or 'nissin_gaccay', the distinctive SiuKay brand font, yellow background, and 'GÀ XỐT PHÔ MAI' label confirm it is siukay_gaphomai_goi.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -9905,20 +14649,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>milo_org_180</t>
+          <t>siukay_bo_goi</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.5962455868721008</v>
+        <v>0.8507356643676758</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>oreo_vanil_105:0.63, pepsi_org_chai_390:0.61, dalatmilk_less_180:0.61, pepsi_org_lon_320:0.61, milo_org_180:0.60</t>
+          <t>siukay_bo_goi:0.85, siukay_gaphomai_goi:0.83, siukay_haisan_goi:0.81, samyang_org_140:0.75, nissin_gaccay:0.74</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The product in the crop shows the characteristic green packaging of the Milo brand. Specifically, the visual elements, color scheme, and the recognizable Milo branding layout match the 'milo_org_180' reference image, which represents the 180ml Milo barley milk drink.</t>
+          <t>The image shows the packaging of 'SiuKay' noodles with the prominent 'SiuKay' logo and the text 'Hương vị Bò' (Beef flavor) with a cartoon cow on the left. Comparing it against the candidate reference images, it matches the packaging of 'siukay_bo_goi' (Mì bò SiuKay gói 127g) exactly in graphics, logo style, and flavor label.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -9938,20 +14682,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mirinda_xaxi_chai_390</t>
+          <t>siukay_haisan_goi</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.5120696425437927</v>
+        <v>0.8475238680839539</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>oreo_vanil_105:0.57, pepsi_org_lon_320:0.54, pepsi_org_chai_390:0.52, pepsi_org_chai_600:0.51, mirinda_xaxi_chai_390:0.51</t>
+          <t>siukay_gaphomai_goi:0.86, siukay_haisan_goi:0.85, siukay_bo_goi:0.82, samyang_org_140:0.74, denhat_thitbam:0.74</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The crop shows a package with visible text 'Mirinda' and 'Xá Xị' (partially visible as 'xaxi'). Comparing this with the provided references, the logo and design match the 'mirinda_xaxi_chai_390' bottle product.</t>
+          <t>The target crop displays the yellow 'SiuKay' logo on a black background along with the text 'Hương vị Hải Sản' (Seafood flavour) and a squid graphic on the left. Comparing this with the reference images, it matches the packaging of 'siukay_haisan_goi' (Mì hải sản SiuKay gói 128g) exactly, ruling out other SiuKay flavors and different brands.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -9970,16 +14714,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.5793892741203308</v>
+        <v>0.7049402594566345</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>pepsi_org_lon_320:0.58, oreo_vanil_105:0.57, dalatmilk_less_180:0.56, pepsi_org_chai_390:0.56, aquafina_5l:0.56</t>
+          <t>samyang_org_140:0.70, omachi_spa_goi:0.70, omachi_tomchuacay_goi:0.70, denhat_thitbam:0.70, siukay_gaphomai_goi:0.70</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The visible part of the product in the crop shows a red and white packaging design with a texture that looks like a food item, possibly a snack or meat product, which does not match the packaging of any of the provided candidates (Pepsi, Oreo, Dalat Milk, or Aquafina).</t>
+          <t>The target image clearly displays the brand 'Omachi' at the top and the product title 'Thần Ớt' along with 'Xốt Cua Ớt'. Comparing this against the plausible candidates, none of the reference images match this specific 'Omachi Thần Ớt Xốt Cua Ớt' product design (the available Omachi options are 'omachi_spa_goi' and 'omachi_tomchuacay_goi'). Therefore, the correct SKU is unknown.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -9999,20 +14743,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>chapagetti_goi_137</t>
+          <t>siukay_gaphomai_goi</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.8342082500457764</v>
+        <v>0.7555497288703918</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>chapagetti_goi_137:0.83, samyang_chacharoni_140:0.76, shin_org_goi_120:0.73, samyang_org_140:0.72, jin_jjajang_goi_135:0.71</t>
+          <t>siukay_gaphomai_goi:0.76, samyang_org_140:0.71, otoki_cheese_cay:0.70, denhat_thitbam:0.70, denhat_photron_cay_goi:0.70</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The crop image shows a pack of 'Chapagetti' with 'Spicy' branding, matching the 'chapagetti_goi_137' reference image. Key features include the 'Nongshim' logo, the large 'Chapagetti' brand text, and the 'SPICY' label on the red background, confirming it is the Nongshim Chapagetti spicy version.</t>
+          <t>Comparing the crop with the candidates, the yellow packaging with the stylized 'SiuKay' logo, the text 'GÀ XỐT PHÔ MAI', and the character design with a chicken holding a chili pepper matches the 'Mì gà cay phô mai SiuKay gói 131g' (siukay_gaphomai_goi) exactly.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -10032,20 +14776,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>siukay_gaphomai_goi</t>
+          <t>siukay_bo_goi</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8905280232429504</v>
+        <v>0.7534814476966858</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>siukay_gaphomai_goi:0.89, siukay_haisan_goi:0.80, siukay_bo_goi:0.80, samyang_org_140:0.73, samyang_cream_carbonara_140:0.73</t>
+          <t>denhat_thitbam:0.76, siukay_bo_goi:0.75, samyang_org_140:0.74, indomie_dacbiet:0.71, samyang_chacharoni_140:0.70</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The crop image shows the yellow packaging of 'SiuKay' branded instant noodles with the text 'GÀ XỐT PHÔ MAI' visible, along with the character graphic matching the 'siukay_gaphomai_goi' reference image exactly.</t>
+          <t>Comparing the crop image with the provided candidates, we can observe the distinct text 'Hương vị Bò' and 'BEEF FLAVOUR' on the left, alongside the cartoon cow breathing fire and the yellow ribbon text 'Ăn dạng MÌ XÀO, MÌ NƯỚC đều ngon! MÌ CAY 7 CẤP ĐỘ'. This matches the packaging design of 'siukay_bo_goi' (Mì bò SiuKay gói 127g) exactly.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -10065,20 +14809,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>siukay_bo_goi</t>
+          <t>indomie_caynong</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8790245056152344</v>
+        <v>0.5805999040603638</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>siukay_bo_goi:0.88, siukay_gaphomai_goi:0.84, siukay_haisan_goi:0.82, samyang_org_140:0.78, samyang_cream_carbonara_140:0.75</t>
+          <t>indomie_caynong:0.58, vnm_org_less_220:0.58, haohao_hanhtim:0.57, denhat_thitbam:0.57, oreo_vanil_105:0.57</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The crop image shows the product packaging with the brand name 'SiuKay' and the text 'Hương vị Bò' (Beef flavor). This matches the reference image for 'siukay_bo_goi' exactly.</t>
+          <t>The crop displays the distinctive blue 'Indomie' logo on a red background along with chili illustrations, matching the Indomie fried noodles packaging. Comparing it with the reference images, it clearly corresponds to 'indomie_caynong' (Mì xào cay nồng Indomie).</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -10098,20 +14842,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lays_tao_nori_53</t>
+          <t>nissin_gaccay</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.5498285293579102</v>
+        <v>0.8309038877487183</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>oreo_vanil_105:0.59, pepsi_org_lon_320:0.57, pepsi_org_chai_390:0.57, dalatmilk_less_180:0.56, lays_tao_nori_53:0.55</t>
+          <t>nissin_gaccay:0.83, samyang_org_140:0.74, siukay_gaphomai_goi:0.73, denhat_thitbam:0.73, otoki_cheese_cay:0.72</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>The crop shows a green packaging with the distinctive Lay's logo and sushi graphic, which matches the Lay's Nori Seaweed (vị tảo biển Nori) product. The text 'Vị Tảo Biển Nori' is visible on the package in the crop, confirming it matches the 'lays_tao_nori_53' reference image.</t>
+          <t>The crop image shows a yellow noodle package with the brand name 'NISSIN' and text reading 'mì cay NISSIN' alongside 'GÀ CÂY PHÔ MAI'. Comparing against the reference images, it matches the packaging of 'nissin_gaccay' (Mì xào Nissin gà cay phô mai Hàn Quốc 72g) exactly, confirming the brand and flavor layout.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -10131,20 +14875,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>siukay_haisan_goi</t>
+          <t>indomie_caynong</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8329233527183533</v>
+        <v>0.7722670435905457</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>siukay_gaphomai_goi:0.84, siukay_haisan_goi:0.83, siukay_bo_goi:0.81, samyang_org_140:0.73, haohao_hanhtim:0.73</t>
+          <t>indomie_dacbiet:0.80, denhat_thitbam:0.78, indomie_caynong:0.77, indomie_hypeabis:0.75, koreno_prem_kimchi:0.72</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>The crop displays the 'SiuKay' brand logo, 'Hương vị Hải Sản' text, and an image of a squid on a black background, which perfectly matches the 'siukay_haisan_goi' reference image.</t>
+          <t>Comparing the crop against the reference images, the package features the distinct Indomie branding and the text 'Mi goreng Pedas' along with 'Mì xào khô vị cay nồng' below it. This matches the indomie_caynong candidate exactly, ruling out indomie_dacbiet and other options which feature different flavor text.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -10162,17 +14906,22 @@
           <t>crop_22_ok.jpg</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>indomie_caynong</t>
+        </is>
+      </c>
       <c r="D24" t="n">
-        <v>0.7279926538467407</v>
+        <v>0.7374692559242249</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>samyang_org_140:0.73, siukay_gaphomai_goi:0.72, denhat_photron_cay_goi:0.72, denhat_thitbam:0.71, haohao_hanhtim:0.71</t>
+          <t>indomie_caynong:0.74, indomie_dacbiet:0.73, denhat_thitbam:0.71, siukay_bo_goi:0.69, samyang_org_140:0.69</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>The crop displays text that reads 'THẦN ỚT' and 'XỐT CUA ỚT'. None of the provided reference images match this branding or flavor. The product name 'THẦN ỚT' is clearly visible in the crop, and it is not among the listed options (Samyang, Siukay, De Nhat, or Hao Hao). Therefore, it must be 'unknown'.</t>
+          <t>The product packaging clearly displays the Indomie logo and the text 'Mi goreng Pedas', matching the design of the Indomie Mi Goreng Pedas (cay nồng) reference image. This rules out all other candidates.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -10192,20 +14941,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>siukay_haisan_goi</t>
+          <t>indomie_caynong</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.7745076417922974</v>
+        <v>0.7994520664215088</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>siukay_gaphomai_goi:0.82, siukay_haisan_goi:0.77, siukay_bo_goi:0.76, denhat_thitbam:0.74, haohao_prem_bosate:0.71</t>
+          <t>indomie_dacbiet:0.82, indomie_caynong:0.80, denhat_thitbam:0.76, indomie_hypeabis:0.76, koreno_prem_kimchi:0.72</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>The visible text on the packaging includes 'SiuKay' and 'An dang MI XAO, MI NUOC deu ngon!'. Among the options, the 'siukay_gaphomai_goi', 'siukay_haisan_goi', and 'siukay_bo_goi' all have this specific branding and descriptive text. However, comparing the background design and the food imagery in the crop with the provided reference images, the specific color and visual style match the 'siukay_haisan_goi' reference, specifically the black background with yellow lightning-like accents, which is distinct from the yellow-orange of the cheese variant or the dark red of the beef variant.</t>
+          <t>Comparing the crop image with the candidate reference images, the product clearly shows 'Mi goreng Pedas' and the text 'vị cay nồng' on a pink and green background, matching the Indomie Mì xào cay nồng packaging exactly. Therefore, the confirmed SKU is indomie_caynong.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -10225,20 +14974,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nissin_gaccay</t>
+          <t>indomie_dacbiet</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.833653450012207</v>
+        <v>0.7703642249107361</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>nissin_gaccay:0.83, samyang_org_140:0.74, siukay_gaphomai_goi:0.72, otoki_cheese_cay:0.72, siukay_haisan_goi:0.71</t>
+          <t>indomie_dacbiet:0.77, indomie_caynong:0.74, denhat_thitbam:0.69, indomie_hypeabis:0.69, koreno_prem_kimchi:0.66</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>The crop image matches the 'nissin_gaccay' reference image perfectly, displaying the 'NISSIN' brand logo, the 'mì cay' branding, and the 'GÀ CAY PHÔ MAI' text, along with the distinct graphic of the chicken and cheese on the packaging.</t>
+          <t>Comparing the crop image against the reference images, the package features the iconic 'Indomie' logo in blue script with a red outline, followed by 'Instant Noodles' in a green banner and 'Mi Goreng' at the bottom. This matches the standard packaging layout of Indomie Mi Goreng variants. Specifically, looking at the color scheme and text formatting, it matches the Indomie Special/Original variant (indomie_dacbiet), showing 'Mi Goreng' without the extra red banner of 'indomie_caynong' or the black packaging of 'indomie_hypeabis'. Therefore, it is 'indomie_dacbiet'.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -10258,20 +15007,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>indomie_caynong</t>
+          <t>indomie_dacbiet</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.7328441739082336</v>
+        <v>0.8403673768043518</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>indomie_caynong:0.73, indomie_dacbiet:0.72, denhat_thitbam:0.71, samyang_org_140:0.68, siukay_bo_goi:0.68</t>
+          <t>indomie_dacbiet:0.84, indomie_caynong:0.78, indomie_hypeabis:0.76, denhat_thitbam:0.76, koreno_prem_kimchi:0.74</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>The crop image shows the packaging of an 'Indomie' instant noodle product. The text 'Mi goreng' and 'cay nong' are visible on the right side of the packaging. Comparing this with the provided candidates, it matches exactly the 'indomie_caynong' (Mì xào cay nồng) product packaging, including the layout and color scheme.</t>
+          <t>The user image shows an Indomie instant noodle packet featuring the distinctive 'Indomie' logo and 'Mi Goreng' text with a picture of fried noodles and a fried egg. Comparing this to the reference candidates, it matches 'indomie_dacbiet' (Mì xào khô đặc biệt Indomie gói 85g) with its classic red, green, and yellow branding rather than the black Ayam Geprek packaging or other completely different brands.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -10291,20 +15040,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>indomie_caynong</t>
+          <t>indomie_dacbiet</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7981555461883545</v>
+        <v>0.8401446938514709</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>indomie_dacbiet:0.81, indomie_caynong:0.80, denhat_thitbam:0.75, indomie_hypeabis:0.75, haohao_mixao_haisan:0.73</t>
+          <t>indomie_dacbiet:0.84, indomie_caynong:0.81, indomie_hypeabis:0.78, denhat_thitbam:0.75, otoki_cheese:0.74</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>The crop displays the Indomie brand and the text 'Mi goreng Pedas' along with 'vị cay nồng' and 'mì xào khô'. Comparing this to the reference images, it matches the packaging of 'indomie_caynong' (Mi xào cay nồng Indomie) exactly, including the specific weight '79g' printed at the bottom.</t>
+          <t>Comparing the query crop against the reference images, we can see the distinctive Indomie logo with blue text and a white outline in the upper left corner. The green band below the red/yellow branding contains the text 'Instant Noodles'. The bottom visible text 'eng' and the bowl of noodles topped with a fried egg directly match the packaging design of the Indomie Mi Goreng variants. Specifically, by comparing with the two most plausible variants (indomie_dacbiet and indomie_caynong), the red-and-white color layout without the bright magenta/pink border of indomie_caynong matches indomie_dacbiet (Mì xào khô đặc biệt Indomie).</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -10324,20 +15073,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>indomie_caynong</t>
+          <t>indomie_dacbiet</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.7637370228767395</v>
+        <v>0.8142271041870117</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>indomie_dacbiet:0.79, denhat_thitbam:0.79, indomie_caynong:0.76, indomie_hypeabis:0.73, koreno_prem_kimchi:0.72</t>
+          <t>indomie_dacbiet:0.81, denhat_thitbam:0.78, indomie_caynong:0.77, indomie_hypeabis:0.73, haohao_mixao_haisan:0.72</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>The crop displays the classic 'Indomie' logo, and the visible text 'Mi goreng' along with the color scheme confirms it is an Indomie product. Comparing it to the reference images, the specific packaging style and the partial Vietnamese text 'cay nồng' (meaning 'spicy') clearly identifies this as the 'indomie_caynong' (Mi xào khô vị cay nồng).</t>
+          <t>Comparing the crop image with the candidate references, we can see the distinctive blue Indomie logo and the red-and-green packaging design. Specifically, the visible text shows 'Mi Goreng' along with the classic Indomie styling. Comparing between 'indomie_dacbiet' and 'indomie_caynong', the layout matches the standard Special Fried Noodles (Mi xào khô Vị đặc biệt). Therefore, it confirms 'indomie_dacbiet'.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -10357,20 +15106,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>indomie_dacbiet</t>
+          <t>haohao_prem_bosate</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8510382175445557</v>
+        <v>0.8602310419082642</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>indomie_dacbiet:0.85, indomie_hypeabis:0.78, indomie_caynong:0.78, denhat_thitbam:0.77, koreno_prem_kimchi:0.73</t>
+          <t>haohao_prem_bosate:0.86, haohao_hanhtim:0.82, haohao_prem_tomchuacay:0.82, haohao_mixao_haisan:0.80, denhat_thitbam:0.79</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>The visible text 'Indomie' and 'Mi Goreng' on the packaging, along with the distinctive color scheme and graphical elements like the egg, match the reference image for 'indomie_dacbiet' exactly.</t>
+          <t>The query image shows a golden packaging featuring the text 'PREMIUM' and 'MÌ TRỘN BÒ SA TẾ', perfectly matching the reference image for 'haohao_prem_bosate' (Mì trộn Hảo Hảo Premium hương vị bò sa tế).</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -10390,20 +15139,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>indomie_dacbiet</t>
+          <t>haohao_prem_bosate</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.8159981369972229</v>
+        <v>0.8739379048347473</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>indomie_dacbiet:0.82, denhat_thitbam:0.77, indomie_caynong:0.76, haohao_mixao_haisan:0.73, indomie_hypeabis:0.73</t>
+          <t>haohao_prem_bosate:0.87, haohao_prem_tomchuacay:0.85, haohao_hanhtim:0.82, haohao_tomchuacay:0.80, haohao_mixao_haisan:0.79</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>The crop displays the characteristic Indomie branding and packaging design for 'Mi Goreng' (Fried Noodles). Comparing it with the reference images, it matches the Indomie 'dacbiet' variant perfectly, specifically the design showing the noodles, the egg, and the 'Mi goreng' text on the red background.</t>
+          <t>The crop image shows the gold packaging with the words 'PREMIUM' and 'HƯƠNG VỊ MÌ TRỘN BÒ SA TẾ'. Comparing this with the candidates, it matches the reference image for 'haohao_prem_bosate' ('Mì trộn Hảo Hảo Premium hương vị bò sa tế gói 88g').</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -10423,20 +15172,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>haohao_prem_bosate</t>
+          <t>haohao_prem_tomchuacay</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.8703043460845947</v>
+        <v>0.8547267913818359</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>haohao_prem_bosate:0.87, haohao_hanhtim:0.83, haohao_prem_tomchuacay:0.82, haohao_mixao_haisan:0.80, haohao_tomchuacay:0.79</t>
+          <t>haohao_prem_tomchuacay:0.85, haohao_prem_bosate:0.85, haohao_hanhtim:0.84, haohao_tomchuacay:0.84, haohao_mixao_haisan:0.81</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>The crop image shows a product with 'PREMIUM' printed prominently, along with the text 'MÌ TRỘN BÒ SA TẾ' and 'Gói súp lớn'. Comparing this to the reference images, it matches the 'haohao_prem_bosate' product exactly in terms of design, text, and flavor branding.</t>
+          <t>The product packaging features the gold background and the bold 'PREMIUM' banner below the 'Hảo Hảo' logo, which matches the Hảo Hảo Premium line. Specifically, the text 'MÌ TÔM CHUA CAY' and 'Gói súp lớn' indicates it is the premium version of the shrimp and sour flavor, exactly matching 'haohao_prem_tomchuacay' (Mì Hảo Hảo Premium tôm chua cay gói 88g).</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -10456,20 +15205,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>haohao_prem_bosate</t>
+          <t>haohao_chay</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.8608794212341309</v>
+        <v>0.8059621453285217</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>haohao_prem_bosate:0.86, haohao_prem_tomchuacay:0.82, haohao_hanhtim:0.82, haohao_tomchuacay:0.80, haohao_mixao_haisan:0.80</t>
+          <t>haohao_mixao_tomchuangot:0.81, haohao_chay:0.81, haohao_mixao_haisan:0.80, haohao_hanhtim:0.79, haohao_tomchuacay:0.77</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The crop image shows 'Hảo Hảo' and 'PREMIUM' branding, along with the text 'HƯƠNG VỊ MÌ TRỘN BÒ SA TẾ'. Comparing this to the reference images, it perfectly matches the 'haohao_prem_bosate' product.</t>
+          <t>The target image clearly displays the brand 'Hảo Hảo' and the text 'Mì Chay' with the flavor label 'hương vị RAU NẤM' on a green packaging background, perfectly matching the reference image for 'haohao_chay'.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -10489,20 +15238,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>haohao_prem_tomchuacay</t>
+          <t>haohao_tomchuacay</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.864803671836853</v>
+        <v>0.8582436442375183</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>haohao_prem_bosate:0.87, haohao_prem_tomchuacay:0.86, haohao_hanhtim:0.84, haohao_tomchuacay:0.83, haohao_mixao_haisan:0.81</t>
+          <t>haohao_tomchuacay:0.86, haohao_hanhtim:0.84, haohao_mixao_haisan:0.82, haohao_mixao_tomchuangot:0.81, haohao_chay:0.79</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>The product in the image is clearly labeled 'PREMIUM' and 'HƯƠNG VỊ MÌ TÔM CHUA CAY'. By comparing this to the provided reference images, it matches the 'haohao_prem_tomchuacay' SKU, which features the same gold and pink color scheme, 'PREMIUM' text, and 'MÌ TÔM CHUA CAY' flavor designation.</t>
+          <t>The target product clearly shows the pink packaging background and the prominent text 'MÌ TÔM CHUA CAY' characteristic of the standard Hảo Hảo tôm chua cay instant noodles. Comparing this with the reference images, it matches the exact design, color theme, and label of the 'haohao_tomchuacay' candidate.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -10522,20 +15271,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>haohao_chay</t>
+          <t>haohao_tomchuacay</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.8178182244300842</v>
+        <v>0.8347377181053162</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>haohao_chay:0.82, haohao_mixao_tomchuangot:0.80, haohao_hanhtim:0.77, haohao_mixao_haisan:0.77, denhat_thitbam:0.76</t>
+          <t>haohao_hanhtim:0.84, haohao_tomchuacay:0.83, haohao_prem_tomchuacay:0.82, haohao_mixao_haisan:0.80, haohao_mixao_tomchuangot:0.80</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>The crop shows a packaging with the text 'Hảo Hảo' and 'Rau Nấm'. This matches the 'Mì Hảo Hảo chay rau nấm' (haohao_chay) product. The visual elements, such as the text 'Rau Nấm' and the overall green theme, are consistent with the haohao_chay reference image.</t>
+          <t>Comparing the query crop against the reference images, we can observe the packaging features clearly. The product has a pink background, features the prominent 'Hảo Hảo' logo, and shows a bowl of noodles with shrimp and vegetables. The text visible on the right says 'MÌ TÔM CHUA...'. Comparing this with the candidates, 'haohao_tomchuacay' features the exact same pink packaging layout with a large shrimp, lime, and chili garnish, matching the visible text 'hương vị MÌ TÔM CHUA CAY'. Therefore, the correct SKU is haohao_tomchuacay.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -10555,20 +15304,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>haohao_tomchuacay</t>
+          <t>koreno_volcano</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.8065701127052307</v>
+        <v>0.8819942474365234</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>haohao_hanhtim:0.82, haohao_tomchuacay:0.81, haohao_mixao_haisan:0.79, haohao_chay:0.79, haohao_mixao_tomchuangot:0.78</t>
+          <t>koreno_volcano:0.88, koreno_prem_kimchi:0.75, samyang_org_140:0.72, siukay_bo_goi:0.70, haohao_mixao_haisan:0.70</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>The crop shows the packaging text 'MÌ TÔM CHUA CAY' and the brand 'Hảo Hảo'. Comparing this to the reference images, the design and text match perfectly with the 'haohao_tomchuacay' reference image.</t>
+          <t>The product crop clearly displays the brand name 'KORENO', the word 'VOLCANO', and the text 'Mì xào' along with 'Vị gà phô mai'. Comparing this with the candidate reference images, it matches the packaging of 'Mì xào Koreno Volcano vị gà phô mai 118g' (koreno_volcano).</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -10588,20 +15337,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>haohao_tomchuacay</t>
+          <t>omachi_spa_goi</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.8692145943641663</v>
+        <v>0.8704688549041748</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>haohao_tomchuacay:0.87, haohao_hanhtim:0.85, haohao_mixao_haisan:0.83, haohao_prem_tomchuacay:0.83, haohao_mixao_tomchuangot:0.82</t>
+          <t>omachi_spa_goi:0.87, omachi_tomchuacay_goi:0.78, omachi_suonham_goi:0.76, denhat_thitbam:0.71, siukay_gaphomai_goi:0.68</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>The crop image shows the packaging of Hảo Hảo Mì Tôm Chua Cay, identifiable by the distinct pink packaging color and the text 'MÌ TÔM CHUA CAY' visible on the right side. The overall graphic, including the shrimp and lime motif, matches the reference image for 'haohao_tomchuacay' exactly.</t>
+          <t>The crop displays the distinctive packaging of Omachi instant noodles with the text 'Xốt Spaghetti' and a visual of spaghetti with cheese and tomato sauce, which matches the 'omachi_spa_goi' reference image precisely.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -10621,20 +15370,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>koreno_volcano</t>
+          <t>haohao_chay</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.9165272116661072</v>
+        <v>0.7918686270713806</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>koreno_volcano:0.92, koreno_prem_kimchi:0.77, samyang_org_140:0.75, samyang_chacharoni_140:0.73, haohao_mixao_haisan:0.73</t>
+          <t>haohao_chay:0.79, haohao_mixao_tomchuangot:0.76, haohao_tomchuacay:0.74, haohao_mixao_haisan:0.74, haohao_hanhtim:0.74</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>The product in the image is clearly labeled 'VOLCANO' and 'Mì xào KORENO'. Comparing this to the reference images, it matches perfectly with 'koreno_volcano', showing the same chicken mascot and color scheme.</t>
+          <t>The product packaging has a green background with the text 'Hảo Hảo' and 'Mì Chay hương vị RAU NẤM'. Comparing this to the reference images, it matches the 'haohao_chay' (Mì Hảo Hảo chay rau nấm 74g) packaging exactly, confirming the correct SKU.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -10654,20 +15403,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>omachi_spa_goi</t>
+          <t>haohao_mixao_tomchuangot</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.8542584776878357</v>
+        <v>0.8483591079711914</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>omachi_spa_goi:0.85, omachi_tomchuacay_goi:0.75, omachi_suonham_goi:0.73, denhat_thitbam:0.71, siukay_gaphomai_goi:0.69</t>
+          <t>haohao_mixao_tomchuangot:0.85, haohao_mixao_haisan:0.81, haohao_hanhtim:0.76, haohao_tomchuacay:0.74, haohao_prem_bosate:0.74</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>The crop shows the packaging of 'Mì trộn Omachi xốt Spaghetti'. Key text elements such as 'Omachi', 'Xốt Spaghetti', 'XỐT BÒ BẦM CÀ CHUA', and 'THÊM GÓI PHÔ MAI' perfectly match the 'omachi_spa_goi' reference image.</t>
+          <t>The product packaging shown in the query crop clearly displays the large text 'Mì Xào' along with the flavor text 'hướng vị Tôm Xào Chua Ngọt' and has a green background design matching the Hảo Hảo tôm chua ngọt dry noodle variant. Comparing it against the reference images, it precisely matches 'haohao_mixao_tomchuangot' rather than other soup or premium variants.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -10687,20 +15436,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>haohao_chay</t>
+          <t>haohao_mixao_haisan</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.8352421522140503</v>
+        <v>0.8871294856071472</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>haohao_chay:0.84, haohao_mixao_tomchuangot:0.77, haohao_tomchuacay:0.77, haohao_hanhtim:0.77, haohao_mixao_haisan:0.77</t>
+          <t>haohao_mixao_haisan:0.89, haohao_mixao_tomchuangot:0.86, haohao_hanhtim:0.83, haohao_tomchuacay:0.81, haohao_prem_bosate:0.80</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The packaging in the provided image clearly displays the text 'Hương vị RAU NẤM', which translates to 'Mushroom and vegetable flavor'. Comparing this with the reference images, it matches the 'haohao_chay' (Mì Hảo Hảo chay rau nấm) product perfectly, which also features a green design and the text 'hương vị RAU NẤM'.</t>
+          <t>The product packaging clearly displays the text "Hảo Hảo" along with "Mì Xào" and "hương vị HẢI SẢN", matching the reference image for haohao_mixao_haisan (Mì xào Hảo Hảo hải sản 75g).</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -10720,20 +15469,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>haohao_mixao_tomchuangot</t>
+          <t>haohao_hanhtim</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.843750536441803</v>
+        <v>0.8765135407447815</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>haohao_mixao_tomchuangot:0.84, haohao_mixao_haisan:0.81, haohao_hanhtim:0.76, haohao_tomchuacay:0.75, haohao_prem_bosate:0.74</t>
+          <t>haohao_hanhtim:0.88, haohao_mixao_haisan:0.81, haohao_tomchuacay:0.78, haohao_prem_bosate:0.78, denhat_thitbam:0.78</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>The crop image shows the packaging for 'Hảo Hảo Mì Xào' with the flavor text 'Tôm Xào Chua Ngọt' clearly visible. This matches the branding, design elements (green and yellow packaging), and product name of the 'haohao_mixao_tomchuangot' reference image.</t>
+          <t>The target image clearly displays the purple packaging of the Hảo Hảo brand with the specific text 'HƯƠNG VỊ SA TẾ HÀNH TÍM'. Comparing it with the reference options, it matches the exact design and flavor text of 'haohao_hanhtim' (Mì Hảo Hảo sa tế hành tím gói 75g).</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -10753,20 +15502,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>haohao_mixao_haisan</t>
+          <t>omachi_tomchuacay_goi</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.8731926083564758</v>
+        <v>0.807537853717804</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>haohao_mixao_haisan:0.87, haohao_mixao_tomchuangot:0.84, haohao_hanhtim:0.83, denhat_thitbam:0.81, haohao_tomchuacay:0.81</t>
+          <t>omachi_tomchuacay_goi:0.81, omachi_suonham_goi:0.77, omachi_spa_goi:0.76, denhat_thitbam:0.68, haohao_hanhtim:0.68</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The crop image shows the product packaging with the text 'Hảo Hảo', 'Mì Xào', and 'hương vị HẢI SẢN'. This matches the reference image for 'haohao_mixao_haisan' perfectly.</t>
+          <t>The product packaging clearly displays the brand name 'Omachi' and the text 'Tôm Càng chua cay' on a green background. Comparing this with the candidates, it matches the 'omachi_tomchuacay_goi' reference image perfectly in terms of colors, typography, and flavor designation.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -10786,20 +15535,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>haohao_hanhtim</t>
+          <t>mi_lauthaitom_goi</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.8718258142471313</v>
+        <v>0.7460700869560242</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>haohao_hanhtim:0.87, haohao_mixao_haisan:0.81, haohao_prem_bosate:0.80, haohao_prem_tomchuacay:0.79, haohao_tomchuacay:0.78</t>
+          <t>mi_lauthaitom_goi:0.75, haohao_prem_tomchuacay:0.66, haohao_tomchuacay:0.66, haohao_big100:0.65, denhat_thitbam:0.63</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>The product in the image is clearly labeled 'hương vị SA TẾ HÀNH TÍM'. Comparing this to the reference images, it matches the design, color scheme, and text of the 'haohao_hanhtim' (Mì Hảo Hảo sa tế hành tím) product exactly.</t>
+          <t>The query crop clearly displays the large text 'LẨU THÁI' and 'Hương vị TÔM' matching the packaging design of 'mi_lauthaitom_goi' (Mì Lẩu Thái tôm gói 81g). Comparing this with other noodle options, the distinct red background, font style, and shrimp imagery confirm it is the Mì Lẩu Thái tôm product.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -10819,20 +15568,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>omachi_tomchuacay_goi</t>
+          <t>omachi_suonham_goi</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.8114017844200134</v>
+        <v>0.8103458285331726</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>omachi_tomchuacay_goi:0.81, omachi_suonham_goi:0.78, omachi_spa_goi:0.73, otoki_yeul_kimchi_goi_100:0.67, denhat_photron_cay_goi:0.67</t>
+          <t>omachi_suonham_goi:0.81, omachi_tomchuacay_goi:0.78, denhat_thitbam:0.77, omachi_spa_goi:0.74, haohao_hanhtim:0.74</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The crop image shows the Omachi brand logo and partial text 'Tôm Càng' and 'chua cay'. This matches the packaging design and product name of the Omachi lẩu tôm càng flavour.</t>
+          <t>The target image clearly displays the 'Omachi' brand name with a black top background and purple-pink lower packaging sections showing the text 'Sườn hầm ngũ quả' and 'Hãy nấu cùng trứng-thịt-rau, rất ngon!'. Comparing this against the reference images, it matches the packaging design of 'omachi_suonham_goi' perfectly.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -10850,22 +15599,17 @@
           <t>crop_43_ok.jpg</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>mi_lauthaitom_goi</t>
-        </is>
-      </c>
       <c r="D45" t="n">
-        <v>0.7828880548477173</v>
+        <v>0.6922498941421509</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>mi_lauthaitom_goi:0.78, haohao_tomchuacay:0.71, denhat_thitbam:0.69, haohao_prem_tomchuacay:0.68, haohao_hanhtim:0.68</t>
+          <t>haohao_tomchuacay:0.69, haohao_prem_tomchuacay:0.69, haohao_big100:0.66, siukay_gaphomai_goi:0.66, lays_wavy_bonuong_53:0.64</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The crop shows text 'LẦU THÁI' and 'Hương vị TÔM' which matches the design of the 'mi_lauthaitom_goi' reference image perfectly.</t>
+          <t>Comparing the crop image with the candidate references, the packaging shows a golden-yellow background with the text 'Tôm Cay Chua' and a cartoon figure at the top wearing a black belt, which uniquely matches the Snack khoai tây Lay's Wavy vị thăn bò nướng Texas or other potato chip designs? Wait, looking closer at the text 'Tôm Cay Chua' and the shrimp imagery, this actually matches a snack version, but let's check the options: none of the standard Hảo Hảo noodle packs have this exact layout, wait, let's examine 'lays_wavy_bonuong_53' or 'unknown'. Actually, the yellow bag with shrimp and a ninja-like character at the top does not match any of the standard Hảo Hảo or SiuKay noodle packages in the references (which have the standard 'Hảo Hảo' red-and-black logo). Since it clearly differs from all provided reference choices, the correct answer is unknown.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -10885,20 +15629,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>omachi_suonham_goi</t>
+          <t>denhat_thitbam</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.7796948552131653</v>
+        <v>0.9066800475120544</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>omachi_suonham_goi:0.78, omachi_tomchuacay_goi:0.76, denhat_thitbam:0.74, denhat_photron_cay_goi:0.71, phuhuong_thitbam_goi:0.71</t>
+          <t>denhat_thitbam:0.91, denhat_photron_bo_goi:0.76, indomie_dacbiet:0.75, denhat_phobo_goi:0.75, denhat_photron_cay_goi:0.74</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>The crop image features the brand 'Omachi' and part of the text 'Sườn' which is clearly visible. Comparing this to the reference images, the design and color scheme (purple and black) match the Omachi Sườn Hầm Ngũ Quả packaging perfectly.</t>
+          <t>The target product clearly shows the brand 'ĐỆ NHẤT' and the text 'MÌ GIA' alongside the flavor label 'THỊT BĂM' (minced meat flavor), matching the packaging design of 'denhat_thitbam'. All other candidates such as 'denhat_phobo_goi' or 'denhat_photron_bo_goi' show different product categories or texts like 'PHỞ BÒ' or 'Phở Trộn', thus they are ruled out.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -10918,20 +15662,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>haohao_tomchuacay</t>
+          <t>mi_lauthaitom_goi</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.6858667731285095</v>
+        <v>0.848402202129364</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>haohao_prem_tomchuacay:0.70, haohao_tomchuacay:0.69, haohao_big100:0.68, siukay_gaphomai_goi:0.67, omachi_tomchuacay_goi:0.65</t>
+          <t>mi_lauthaitom_goi:0.85, haohao_tomchuacay:0.74, haohao_hanhtim:0.73, denhat_thitbam:0.72, haohao_mixao_haisan:0.72</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The crop displays the characteristic design of the Hảo Hảo brand's Tom Cay Chua flavour. Specifically, the logo text 'Hảo Hảo' and the large text 'Tom Cay Chua' with the imagery of a prawn are identical to the 'haohao_tomchuacay' reference. The specific composition of the ingredients (shrimp, lime slice) and the font style on the packaging match the standard Hảo Hảo 75g package.</t>
+          <t>The product packaging clearly displays the text "MÌ LẨU THÁI" along with "HƯƠNG VỊ TÔM" and shows the distinctive design of the Mì Lẩu Thái tôm gói. This directly matches the reference image for mi_lauthaitom_goi and differs from all other Hảo Hảo or Đệ Nhất candidates.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -10951,20 +15695,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>denhat_thitbam</t>
+          <t>udon_sukisuki_tron</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.9126074910163879</v>
+        <v>0.7371249198913574</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>denhat_thitbam:0.91, denhat_phobo_goi:0.76, denhat_photron_bo_goi:0.76, denhat_photron_cay_goi:0.75, haohao_mixao_haisan:0.75</t>
+          <t>udon_sukisuki_tron:0.74, udon_sukisuki_goi:0.68, haohao_prem_bosate:0.60, denhat_photron_bo_goi:0.59, haohao_prem_tomchuacay:0.58</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>The crop image shows the text 'ĐỆ NHẤT', 'MÌ GIA', and 'THỊT BẰM'. Comparing this with the provided reference images, it matches exactly with the packaging design, branding, and flavor label of the 'denhat_thitbam' (Mì Đệ Nhất thịt bằm) product.</t>
+          <t>The crop displays the brand name 'Udon', the sub-brand 'SUKISUKI', and the text 'Trộn' along with 'HƯƠNG VỊ BÒ XỐT TERIYAKI'. Comparing this against the candidate reference images, it matches the packaging of 'udon_sukisuki_tron' exactly, ruling out all other soups or noodle types.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -10984,20 +15728,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mi_lauthaitom_goi</t>
+          <t>udon_sukisuki_tron</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.8527869582176208</v>
+        <v>0.8335797786712646</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>mi_lauthaitom_goi:0.85, haohao_tomchuacay:0.73, denhat_thitbam:0.73, haohao_hanhtim:0.73, haohao_mixao_haisan:0.72</t>
+          <t>udon_sukisuki_tron:0.83, udon_sukisuki_goi:0.73, denhat_photron_cay_goi:0.71, denhat_photron_bo_goi:0.71, haohao_prem_bosate:0.71</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>The crop image shows the text 'MÌ LẤU THÁI' and 'Hương vị TÔM', which matches exactly with the reference image for 'mi_lauthaitom_goi'.</t>
+          <t>The product image clearly shows the brand name 'Udon', 'SUKISUKI', and the word 'Trộn' along with the flavor 'HƯƠNG VỊ BÒ XỐT TERIYAKI'. Comparing this against the candidate 'udon_sukisuki_tron', all textual elements and the visual design of the packaging match exactly.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -11021,16 +15765,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.8536402583122253</v>
+        <v>0.8255548477172852</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>udon_sukisuki_tron:0.85, udon_sukisuki_goi:0.77, denhat_photron_bo_goi:0.74, denhat_photron_cay_goi:0.73, haohao_prem_bosate:0.72</t>
+          <t>udon_sukisuki_tron:0.83, udon_sukisuki_goi:0.77, denhat_photron_bo_goi:0.70, vifon_bocay_goi:0.70, denhat_thitbam:0.69</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>The crop image shows the product 'Udon' with 'SUKISUKI' branding, 'Trộn' (mixed noodles) text, and 'HƯƠNG VỊ BÒ XỐT TERIYAKI'. Comparing this to the provided reference images, it is an exact match for the 'udon_sukisuki_tron' SKU.</t>
+          <t>The crop clearly shows the large black text 'Udon', 'SUKISUKi', and 'Trộn', along with 'HƯƠNG VỊ BÒ XỐT TERIYAKI'. Comparing this with the candidates, it matches the packaging of 'udon_sukisuki_tron' (Mì Udon Sưkisưki trộn hương vị bò xốt teriyaki gói 82g) perfectly, distinguishing it from 'udon_sukisuki_goi' which is the soup version.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -11050,20 +15794,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>udon_sukisuki_tron</t>
+          <t>haohao_big100</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.805508553981781</v>
+        <v>0.8834933042526245</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>udon_sukisuki_tron:0.81, udon_sukisuki_goi:0.74, denhat_photron_bo_goi:0.69, vifon_bocay_goi:0.67, haohao_prem_bosate:0.67</t>
+          <t>haohao_big100:0.88, haohao_hanhtim:0.82, haohao_tomchuacay:0.81, haohao_mixao_haisan:0.81, haohao_prem_tomchuacay:0.80</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>The crop shows the text 'Udon', 'SUKISUKI', and 'Trộn' as well as 'HƯƠNG VỊ BÒ XỐT TERIYAKI'. This perfectly matches the packaging design and labels of the udon_sukisuki_tron reference image.</t>
+          <t>The product packaging clearly displays 'BIG 100 g' below the Hảo Hảo brand name and features the pink-themed design associated with the Hảo Hảo Big 100g hot-sour shrimp flavor. Comparing it with the references, it matches the 'haohao_big100' candidate.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -11083,20 +15827,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>haohao_big100</t>
+          <t>vifon_bocay_goi</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.8857532143592834</v>
+        <v>0.8979770541191101</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>haohao_big100:0.89, haohao_tomchuacay:0.83, haohao_hanhtim:0.83, haohao_mixao_haisan:0.82, haohao_prem_tomchuacay:0.80</t>
+          <t>vifon_bocay_goi:0.90, vifon_rieucua_goi:0.75, denhat_thitbam:0.72, udon_sukisuki_tron:0.71, denhat_photron_cay_goi:0.70</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>The image clearly shows the packaging for 'Hảo Hảo BIG' with '100g' prominently displayed. Comparing this to the candidate reference images, it matches the 'haohao_big100' packaging, which features the large 'BIG 100g' text and the 'TĂNG HƠN 30%' starburst graphic.</t>
+          <t>The crop clearly shows the VIFON logo and packaging text 'MÌ THỊT THẬT' along with 'BÒ CAY'. Comparing this to the candidates, it matches the 'vifon_bocay_goi' reference image perfectly in branding, text layout, and overall design.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -11116,20 +15860,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>vifon_bocay_goi</t>
+          <t>vifon_rieucua_goi</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.9174304604530334</v>
+        <v>0.8673701286315918</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>vifon_bocay_goi:0.92, vifon_rieucua_goi:0.76, denhat_thitbam:0.73, udon_sukisuki_tron:0.71, denhat_phobo_goi:0.71</t>
+          <t>vifon_rieucua_goi:0.87, vifon_bocay_goi:0.72, phuhuong_suonheo_goi:0.69, denhat_thitbam:0.68, udon_sukisuki_goi:0.68</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The crop displays the Vifon brand logo and the text 'MÌ BÒ CAY' and 'THỊT THẬT', which matches the 'vifon_bocay_goi' reference image perfectly. The design, including the bowl of noodles and the placement of the text, is identical.</t>
+          <t>The product packaging clearly displays the brand 'VIFON' and the prominent text 'Mì Riêu Cua' along with English subtext 'INSTANT NOODLES WITH CRAB SOUP'. Comparing this directly with the reference images, it matches the 'vifon_rieucua_goi' candidate perfectly in terms of text, font, color scheme, and imagery.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -11153,16 +15897,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.8894175887107849</v>
+        <v>0.7280822992324829</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>vifon_rieucua_goi:0.89, denhat_thitbam:0.74, vifon_bocay_goi:0.74, otoki_cheese_cay:0.73, udon_sukisuki_goi:0.72</t>
+          <t>vifon_rieucua_goi:0.73, otoki_cheese_cay:0.64, denhat_thitbam:0.63, samyang_chacharoni_140:0.62, shin_org_goi_120:0.62</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The product image clearly shows the 'VIFON' brand logo and the text 'Mì Riêu Cua' along with the English subtitle 'CRAB SOUP'. This matches the reference image for 'vifon_rieucua_goi' perfectly, including the packaging design, font, and imagery.</t>
+          <t>Comparing the crop image with the candidate options, the text 'CRAB SOU' and 'CUA THẬT' along with the specific packaging design uniquely identify the product as vifon_rieucua_goi (Mì Vifon riêu cua gói 90g).</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -11182,20 +15926,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>vifon_rieucua_goi</t>
+          <t>denhat_phobo_goi</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.7097520232200623</v>
+        <v>0.6321252584457397</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>vifon_rieucua_goi:0.71, otoki_cheese_cay:0.62, shin_org_goi_120:0.61, denhat_thitbam:0.61, samyang_org_140:0.61</t>
+          <t>denhat_phobo_goi:0.63, denhat_photron_bo_goi:0.57, denhat_thitbam:0.56, denhat_photron_cay_goi:0.54, haohao_prem_tomchuacay:0.49</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>The crop image shows the text 'CRAB SOU' (part of CRAB SOUP) and 'VIFON'. It also shows a badge with the text 'CÓ GÓI CUA THẬT' and a specific medal design that matches the reference image for 'vifon_rieucua_goi'. Other candidates are completely different in brand and packaging design.</t>
+          <t>The crop displays the red packaging of 'ĐỆ NHẤT PHỞ' with the prominent text 'PHỞ BÒ' written in white, matching the reference image for 'denhat_phobo_goi'.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -11219,16 +15963,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.8382065892219543</v>
+        <v>0.8237276077270508</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>denhat_photron_cay_goi:0.84, denhat_photron_bo_goi:0.81, denhat_thitbam:0.80, denhat_phobo_goi:0.78, haohao_hanhtim:0.77</t>
+          <t>denhat_photron_cay_goi:0.82, denhat_thitbam:0.79, denhat_photron_bo_goi:0.79, denhat_phobo_goi:0.77, haohao_hanhtim:0.74</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>The crop shows packaging with the text 'ĐỆ NHẤT', 'PHỞ', and 'THẬP CẨM CAY'. This matches the packaging design and product name of the 'denhat_photron_cay_goi' candidate.</t>
+          <t>Comparing the crop image with the candidate references, we can see the packaging has a red header with the 'ĐỆ NHẤT PHỞ' logo, and the large white-and-red text 'Phở Trộn' with the label 'THẬP CẨM CAY'. This matches the 'denhat_photron_cay_goi' reference (Phở trộn Đệ Nhất vị thập cẩm cay gói 84g), whereas other options like beef or mincemeat show different flavor texts or brands.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -11252,16 +15996,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.8567149639129639</v>
+        <v>0.8619568347930908</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>denhat_phobo_goi:0.86, denhat_photron_bo_goi:0.75, denhat_thitbam:0.75, denhat_photron_cay_goi:0.74, omachi_tomchuacay_goi:0.70</t>
+          <t>denhat_phobo_goi:0.86, denhat_photron_bo_goi:0.76, denhat_thitbam:0.74, denhat_photron_cay_goi:0.74, haohao_prem_tomchuacay:0.69</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>The product in the crop clearly shows the text 'PHỞ BÒ' and 'ĐỆ NHẤT', matching the 'denhat_phobo_goi' candidate. The packaging design features the characteristic dark red background, '12h' logo, and bowl of soup, which aligns perfectly with the provided reference image for 'denhat_phobo_goi'.</t>
+          <t>The target crop clearly shows the packaging for 'ĐỆ NHẤT PHỞ BỎ' with the red background, bowl of phở with beef and green onions on the right, and the distinct '12h' logo. This matches the reference image 'denhat_phobo_goi' exactly in all text, color scheme, and graphic layout.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -11285,16 +16029,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.753035306930542</v>
+        <v>0.7560487985610962</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>phuhuong_thitbam_goi:0.75, denhat_thitbam:0.74, phuhuong_suonheo_goi:0.72, nhipsong_namvang:0.71, denhat_photron_bo_goi:0.67</t>
+          <t>phuhuong_thitbam_goi:0.76, denhat_thitbam:0.73, phuhuong_suonheo_goi:0.72, nhipsong_namvang:0.71, omachi_suonham_goi:0.67</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The product in the crop shows the brand name 'Miến Phú Hương' and the flavor text 'THỊT BẰM'. Comparing this to the reference images, it matches exactly with the packaging of the 'phuhuong_thitbam_goi' SKU.</t>
+          <t>The product packaging shown in the query features the brand text 'Miến Phú Hương' and the flavor text 'Hương vị THỊT BĂM', which matches the reference image for 'phuhuong_thitbam_goi'. Other candidates like 'phuhuong_suonheo_goi' have a green background and different flavor text. Thus, the correct SKU is phuhuong_thitbam_goi.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -11318,16 +16062,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.7130369544029236</v>
+        <v>0.7426595687866211</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>phuhuong_suonheo_goi:0.71, phuhuong_thitbam_goi:0.69, haohao_mixao_tomchuangot:0.67, denhat_thitbam:0.65, haohao_chay:0.63</t>
+          <t>phuhuong_suonheo_goi:0.74, phuhuong_thitbam_goi:0.70, haohao_mixao_tomchuangot:0.70, haohao_chay:0.67, denhat_thitbam:0.66</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>The crop image shows a product with 'Miến Phú Hương' and 'Hương vị SƯỜN HEO' text. By comparing this to the reference images, it matches the 'phuhuong_suonheo_goi' product exactly in terms of design, logo, and flavor text.</t>
+          <t>The target product clearly shows the green packaging of 'Miến Phú Hương' with the text 'Hương vị SƯỜN HEO' and 'SPARERIBS FLAVOUR'. Comparing it with the reference images, it matches the 'phuhuong_suonheo_goi' candidate perfectly.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -11351,16 +16095,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.8100965619087219</v>
+        <v>0.80184006690979</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>nhipsong_namvang:0.81, denhat_thitbam:0.74, phuhuong_suonheo_goi:0.74, phuhuong_thitbam_goi:0.73, haohao_prem_bosate:0.72</t>
+          <t>nhipsong_namvang:0.80, phuhuong_suonheo_goi:0.75, phuhuong_thitbam_goi:0.74, denhat_photron_cay_goi:0.73, haohao_prem_bosate:0.73</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The crop displays the branding 'Nhịp Sống' and the text 'Hủ Tiếu Nam Vang', which matches exactly with the reference image for 'nhipsong_namvang'.</t>
+          <t>The query image clearly displays the brand logo 'Nhịp Sống' and the text 'Hủ Tiếu Nam Vang' on a dark blue and yellow background matching the reference image 'nhipsong_namvang'. Therefore, it is definitively the Nhịp Sống Hủ Tiếu Nam Vang product.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -11380,20 +16124,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>phuhuong_suonheo_goi</t>
+          <t>denhat_phobo_goi</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.6989503502845764</v>
+        <v>0.706009566783905</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>phuhuong_suonheo_goi:0.70, phuhuong_thitbam_goi:0.69, denhat_thitbam:0.64, denhat_phobo_goi:0.62, milo_org_180:0.62</t>
+          <t>denhat_phobo_goi:0.71, denhat_thitbam:0.69, haohao_hanhtim:0.65, haohao_prem_tomchuacay:0.65, denhat_photron_cay_goi:0.65</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>The crop shows the 'Miến Phú Hương' brand name and parts of the packaging with green color tones. Comparing this with the candidates, the product design matches the 'phuhuong_suonheo_goi' (Miến Phú Hương sườn heo) reference image, specifically the green background and the 'Miến Phú Hương' branding style.</t>
+          <t>The crop displays the text 'XƯƠNG THỊT THẬT HẦM' and the 12h badge, which matches the 'ĐỆ NHẤT PHỞ PHỞ BÒ' packaging. Comparing it with the candidates, it clearly features the exact red banner and layout of denhat_phobo_goi rather than the mixed noodle variation or other brands.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
